--- a/セリフ編集/キャラタイプ別/標準×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×お気楽.xlsx
@@ -1927,7 +1927,7 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分けだって。ちょうどいいんじゃない?</t>
+          <t xml:space="preserve">決着つかずだって。ちょうどいいんじゃない?</t>
         </is>
       </c>
     </row>

--- a/セリフ編集/キャラタイプ別/標準×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×お気楽.xlsx
@@ -372,7 +372,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -430,22 +430,22 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.standard.hit[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.standard.hit[1]</t>
+          <t xml:space="preserve">atk.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -455,29 +455,29 @@
       </c>
       <c r="F2" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うわ、効く…でも、ここで沈むのは違うんだよね。</t>
+          <t xml:space="preserve">あはは、楽しくなってきた！</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.standard.hit[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.standard.hit[2]</t>
+          <t xml:space="preserve">atk.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -487,29 +487,29 @@
       </c>
       <c r="F3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もうちょい踏ん張らせて。あそこに見せたい景色があるの。</t>
+          <t xml:space="preserve">いい試合にしようよ！</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.standard.win[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.standard.win[1]</t>
+          <t xml:space="preserve">atk.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -519,29 +519,29 @@
       </c>
       <c r="F4" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">要らないって言われた側なんだけどさ、勝っちゃった。いいの?</t>
+          <t xml:space="preserve">まだまだいけるよ〜！</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.standard.win[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.easygoing[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.standard.win[2]</t>
+          <t xml:space="preserve">atk.standard.easygoing[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -551,1036 +551,3916 @@
       </c>
       <c r="F5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あそこ、私を切ったの…ちょっと早まったんじゃない?</t>
+          <t xml:space="preserve">本気出しちゃうよ？</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.lose[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.lose[1]</t>
+          <t xml:space="preserve">bigmove.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃいました。ごめんなさい。</t>
+          <t xml:space="preserve">よーし、ここで決めちゃおう！</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.lose[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.lose[2]</t>
+          <t xml:space="preserve">bigmove.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">だめでした。まあ、また誘えばいいですよね。</t>
+          <t xml:space="preserve">いっくよー！ 最後の大技！</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.lose[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.lose[3]</t>
+          <t xml:space="preserve">bigmove.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました。でも、後悔はしてないです。</t>
+          <t xml:space="preserve">えへへ…全力いくよー！</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.petition[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.petition[1]</t>
+          <t xml:space="preserve">climax.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あの人とやってみたいんですけど、どうですか。</t>
+          <t xml:space="preserve">（わくわくする…この瞬間が一番好き）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.petition[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.petition[2]</t>
+          <t xml:space="preserve">climax.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">だめならいいんです。でも、あの人とやりたくて。</t>
+          <t xml:space="preserve">（最高の試合にしよう！）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.petition[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.petition[3]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんとなく、あの人とやりたくなっちゃって。</t>
+          <t xml:space="preserve">あたた…でもまだ大丈夫！</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.sendoff[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.sendoff[1]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。じゃあ、行ってきますね。</t>
+          <t xml:space="preserve">う〜ん…効いたかも…でもへーきへーき！</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.sendoff[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.sendoff[2]</t>
+          <t xml:space="preserve">standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、いいんですか。ありがとうございます。</t>
+          <t xml:space="preserve">いたた…ちょっと休憩…なんてね！</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.sendoff[3]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.easygoing.hit[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.sendoff[3]</t>
+          <t xml:space="preserve">standard.easygoing.hit[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。楽しんできます。</t>
+          <t xml:space="preserve">うわ、効く…でも、ここで沈むのは違うんだよね。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.easygoing.hit[2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.win[1]</t>
+          <t xml:space="preserve">standard.easygoing.hit[2]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました。案外、いけるもんですね。</t>
+          <t xml:space="preserve">もうちょい踏ん張らせて。あそこに見せたい景色があるの。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.easygoing.win[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.win[2]</t>
+          <t xml:space="preserve">standard.easygoing.win[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった、勝ちました。言ってよかったです。</t>
+          <t xml:space="preserve">要らないって言われた側なんだけどさ、勝っちゃった。いいの?</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.win[3]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.easygoing.win[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.win[3]</t>
+          <t xml:space="preserve">standard.easygoing.win[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちましたよ。ちゃんと帰ってきました。</t>
+          <t xml:space="preserve">あそこ、私を切ったの…ちょっと早まったんじゃない?</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing._accept[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing._accept[1]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしでいいの? いいよ、やろっか。</t>
+          <t xml:space="preserve">ありゃ…動けない…</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing._accept[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing._accept[2]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずいぶん熱心だね。まあ、受けるよ。</t>
+          <t xml:space="preserve">うぅ…遠い…</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing._accept[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing._accept[3]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そんなに力まなくても、ちゃんと相手するって。</t>
+          <t xml:space="preserve">させないよ〜！</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.draw[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.draw[1]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着つかずだって。ちょうどいいんじゃない?</t>
+          <t xml:space="preserve">まだまだ〜！</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.draw[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.draw[2]</t>
+          <t xml:space="preserve">standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決まらなかったね。まあ、またそのうち。</t>
+          <t xml:space="preserve">はい、カット！</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.draw[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.draw[3]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お互い元気だねえ。ちょっと疲れた。</t>
+          <t xml:space="preserve">一緒にやろ〜！</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.lose[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.lose[1]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃった。まあ、そういう日もあるよ。</t>
+          <t xml:space="preserve">合わせて合わせて♪</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.lose[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.lose[2]</t>
+          <t xml:space="preserve">standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたの勝ち。おめでとう。</t>
+          <t xml:space="preserve">せーのっ♪</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.lose[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.lose[3]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やられたなあ。……次はもうちょっと粘る。</t>
+          <t xml:space="preserve">はーい、交代〜！</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.win[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.win[1]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っちゃった。……そんな顔しないでよ。</t>
+          <t xml:space="preserve">お疲れさま♪ 私いくね</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.win[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.win[2]</t>
+          <t xml:space="preserve">standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受けてよかったな。楽しかったよ。</t>
+          <t xml:space="preserve">ここからは私の出番♪</t>
         </is>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.win[3]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_easygoing.win[3]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">案外あっさりだったね。次はもっと粘って。</t>
+          <t xml:space="preserve">{partner}〜ごめんね…私、決められちゃった…</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES.easygoing.standard[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.standard[1]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー、まあ、一緒にやるのはちょっと無理かな。向こうとは、別で。</t>
+          <t xml:space="preserve">あちゃ〜負けちゃった…でも{partner}、次は頑張るね。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.easygoing.standard[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.standard[1]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……えっ。……ちょっと、待って。頭、追いつかない……。</t>
+          <t xml:space="preserve">{partner}〜お疲れさま！ 私たち、息ぴったりだったね〜</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.easygoing.standard[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.standard[1]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">んー、なんかさ、流れでこっちの方が楽しいんだよね。悪く思わないでよ。</t>
+          <t xml:space="preserve">勝っちゃった。{partner}と組むの、やっぱ楽しい〜</t>
         </is>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.easygoing.standard[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.lose[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.standard[1]</t>
+          <t xml:space="preserve">standard_easygoing.lose[1]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えー社長、ちょっと、うちの子らに甘くしてくんない？</t>
+          <t xml:space="preserve">負けちゃいました。ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.easygoing.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.lose[2]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.standard.high[1]</t>
+          <t xml:space="preserve">standard_easygoing.lose[2]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんとかなったね、よかった</t>
+          <t xml:space="preserve">だめでした。まあ、また誘えばいいですよね。</t>
         </is>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.easygoing.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.lose[3]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.standard.high[1]</t>
+          <t xml:space="preserve">standard_easygoing.lose[3]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">とりあえず1つ、もらった</t>
+          <t xml:space="preserve">負けました。でも、後悔はしてないです。</t>
         </is>
       </c>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.easygoing.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.petition[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.standard.high[1]</t>
+          <t xml:space="preserve">standard_easygoing.petition[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、ここまで来ちゃったしね。今夜決めようよ</t>
+          <t xml:space="preserve">社長、あの人とやってみたいんですけど、どうですか。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.easygoing.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.petition[2]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.petition[2]</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">だめならいいんです。でも、あの人とやりたくて。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.petition[3]</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.petition[3]</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">なんとなく、あの人とやりたくなっちゃって。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.sendoff[1]</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.sendoff[1]</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとうございます。じゃあ、行ってきますね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.sendoff[2]</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.sendoff[2]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わ、いいんですか。ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.sendoff[3]</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.sendoff[3]</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとうございます。楽しんできます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.win[1]</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.win[1]</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝てました。案外、いけるもんですね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.win[2]</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.win[2]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やった、勝ちました。言ってよかったです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_easygoing.win[3]</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.win[3]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちましたよ。ちゃんと帰ってきました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing._accept[1]</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing._accept[1]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたしでいいの? いいよ、やろっか。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing._accept[2]</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing._accept[2]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ずいぶん熱心だね。まあ、受けるよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing._accept[3]</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing._accept[3]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">そんなに力まなくても、ちゃんと相手するって。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.draw[1]</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.draw[1]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決着つかずだって。ちょうどいいんじゃない?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.draw[2]</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.draw[2]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決まらなかったね。まあ、またそのうち。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.draw[3]</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.draw[3]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お互い元気だねえ。ちょっと疲れた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.lose[1]</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.lose[1]</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けちゃった。まあ、そういう日もあるよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.lose[2]</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.lose[2]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あなたの勝ち。おめでとう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.lose[3]</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.lose[3]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やられたなあ。……次はもうちょっと粘る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.win[1]</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.win[1]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝っちゃった。……そんな顔しないでよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.win[2]</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.win[2]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">受けてよかったな。楽しかったよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_easygoing.win[3]</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_easygoing.win[3]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">案外あっさりだったね。次はもっと粘って。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長〜、私たちの子のこと、忘れないでくださいね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長〜、次のメイン、私たちでいきましょうよ。盛り上げますって。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長〜、お給料の話なんですけど、ちょっとだけ上げてもらえませんか?</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長〜、私たちの頑張り、たまには褒めてくれてもいいんですよ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わ、ちゃんと聞いてくれてた! 嬉しいです、ありがとうございます〜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、はーい。…まあ、社長忙しいですもんね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふぅん、別ルートですか〜。まあ、ありがたいですけど。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やった、社長ありがとう! メイン張りますね!</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">えぇ〜、まあ、わかりましたけど〜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふぅん、そっちですか〜。まあいいですけど。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">えっ、ホントに上げてくれるんですか? やった〜! みんなに自慢しちゃう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">えぇ〜、まあ仕方ないですよね〜。次に期待してます〜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あれ、お金の話そらされた? でもまあ、ありがとうございます〜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ホント!? やった、社長に褒められちゃった〜!</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="40" customHeight="1">
+      <c r="A71" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">えぇ〜、つれないなぁ〜。まあいいですけど。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="40" customHeight="1">
+      <c r="A72" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">なるほど〜、評価は別の形でってことですね。了解です〜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="40" customHeight="1">
+      <c r="A73" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">え、そんなに気にしてました? ごめんなさ〜い、次は誘いますって。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="40" customHeight="1">
+      <c r="A74" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとうございま〜す、楽しんでこまーす。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="40" customHeight="1">
+      <c r="A75" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、そっか〜、気をつけまーす。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="40" customHeight="1">
+      <c r="A76" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとうございま〜す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="40" customHeight="1">
+      <c r="A77" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">えぇ〜、客もノッてたじゃないですか〜。…はーい、控えまーす。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="40" customHeight="1">
+      <c r="A78" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やった〜、社長わかってる〜! 引き続き暴れまーす。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="40" customHeight="1">
+      <c r="A79" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、ばれてました? すみませ〜ん、明日から出ますって。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="40" customHeight="1">
+      <c r="A80" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お、見逃してくれるんですか〜? 助かります〜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="40" customHeight="1">
+      <c r="A81" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふぅん、メンバーケア優先ですか〜。まあ、それでいいです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="40" customHeight="1">
+      <c r="A82" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">えへへ、バレてた? じゃ、お言葉に甘えて休みまーす。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="40" customHeight="1">
+      <c r="A83" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いや〜、まだいけますって〜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="40" customHeight="1">
+      <c r="A84" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お、メンバーケアですか? 助かりますね〜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="40" customHeight="1">
+      <c r="A85" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">えー、序列の話なんてしてないですよ〜。…まあ、注意しときますけど。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="40" customHeight="1">
+      <c r="A86" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふぅん、まあ放っておいてくれるなら〜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="40" customHeight="1">
+      <c r="A87" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お、別ルートですか。下の子のフォロー、お願いします〜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="40" customHeight="1">
+      <c r="A88" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あー、はい、注意します〜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="40" customHeight="1">
+      <c r="A89" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">（へらっと笑って、話を流した）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="40" customHeight="1">
+      <c r="A90" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">そっち経由ですか〜。了解です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="40" customHeight="1">
+      <c r="A91" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">えぇ〜、これくらい大丈夫なんですけどぉ。…はぁい、緩めま〜す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="40" customHeight="1">
+      <c r="A92" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お、続けていいんですね〜! やった〜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="40" customHeight="1">
+      <c r="A93" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あれ、私じゃなくて子たち優先? まあ、ありがたいですけど〜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="40" customHeight="1">
+      <c r="A94" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.attack.standard</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.attack.standard</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">仲良しごっこは終わり、かな</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="40" customHeight="1">
+      <c r="A95" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.defend.standard</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.defend.standard</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、仕方ないよね</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="40" customHeight="1">
+      <c r="A96" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr" s="2">
+      <c r="C96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まー、なんていうか、ちょっと合わないんだよね、もう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="40" customHeight="1">
+      <c r="A97" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あはは、もう何で揉めてたんだっけ、あたしたち。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">はぁ〜あ、こうなると、もうやるしかないよね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.easygoing.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ〜あ、負けちゃった。ま、こんな日もあるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.easygoing.hp_high[2]</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.hp_high[2]</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うん、負け。次はもうちょっと頑張る</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.easygoing.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">（うつぶせのまま動かない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.easygoing.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……いた……っ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ〜あ、勝っちゃった。次は仲良くやろうよ、本気で</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.easygoing.high[2]</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.high[2]</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝つには勝ったけど、あんたんとこも、もう静かにしとこ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.easygoing.low[1]</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.low[1]</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝てたみたい。ふぅ</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.easygoing.mid[1]</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.mid[1]</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">んー、勝った。それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">んー、こうなっちゃったら、もう仕方ないよね。やろっか</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.easygoing.high[2]</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.high[2]</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あたしも嫌なんだけど、組のみんなが黙ってないから</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="40" customHeight="1">
+      <c r="A109" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.easygoing.low[1]</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.low[1]</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やれやれ……一回、ぶつかっとくか</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.easygoing.mid[1]</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.mid[1]</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、リングで決めようよ。それが一番すっきりする</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ〜あ、こうなっちゃったか。仕方ない、付き合うよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.easygoing.high[2]</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.high[2]</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">断りたいけど、断れる空気じゃないもんね、これ</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.easygoing.low[1]</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.low[1]</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">んー、付き合います</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.easygoing.mid[1]</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.mid[1]</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、いっか。リングで決めようよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES.standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">はー、やられたなあ。組み立て直しだね</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">なんとかなったね、よかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES.standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……うわ、負けた。次よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">とりあえず1つ、もらった</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES.standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やろっか</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まあ、ここまで来ちゃったしね。今夜決めようよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing.standard.high[1]</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr" s="3">
+      <c r="D121" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">やれやれ……じゃあ、行こうか</t>
         </is>
       </c>
     </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.easygoing.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">はー、抜かれちゃったか。次の子、頑張れよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.easygoing.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……参った</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.easygoing.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やられたなあ、参った参った</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES.standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あー、勝っちゃったか。じゃ、頑張りますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やー、こういう日も来るよね。じゃ、行こうか</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing.high[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">おう、来るかい。じゃあ行こう</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H37"/>
+  <autoFilter ref="A1:H127"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×お気楽.xlsx
@@ -279,34 +279,34 @@
     <row r="6">
       <c r="A6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">早川モナ</t>
+          <t xml:space="preserve">小森さなえ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Aerial</t>
+          <t xml:space="preserve">Brawler</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Babyface</t>
+          <t xml:space="preserve">Neutral</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">華、負けず嫌い</t>
+          <t xml:space="preserve">ムードメーカー</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">海老名栞</t>
+          <t xml:space="preserve">早川モナ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Submission</t>
+          <t xml:space="preserve">Aerial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
@@ -316,7 +316,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ファンサービス、ライバル体質、野心</t>
+          <t xml:space="preserve">華、負けず嫌い</t>
         </is>
       </c>
     </row>
@@ -372,7 +372,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H474"/>
+  <dimension ref="A1:H476"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="F35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">要らないって言われた側なんだけどさ、勝っちゃった。いいの?</t>
+          <t xml:space="preserve">要らないって言われた側なんだけどさ、勝っちゃった。いいの？</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="F36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あそこ、私を切ったの…ちょっと早まったんじゃない?</t>
+          <t xml:space="preserve">あそこ、私を切ったの…ちょっと早まったんじゃない？</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんな綺麗に忘れてるね。……あたしは忘れないけど</t>
+          <t xml:space="preserve">みんな綺麗に忘れてるね。……私は忘れないけど</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おう！ 最高の締めにしようぜ！</t>
+          <t xml:space="preserve">最高の締めにしよう！ さあ、行くよ！</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしでいいの? いいよ、やろっか。</t>
+          <t xml:space="preserve">私でいいの？ いいよ、やろっか。</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着つかずだって。ちょうどいいんじゃない?</t>
+          <t xml:space="preserve">決着つかずだって。ちょうどいいんじゃない？</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ…あたし邪魔なの？ ちょっとひどくない？</t>
+          <t xml:space="preserve">えぇ…私邪魔なの？ ちょっとひどくない？</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、お給料の話なんですけど、ちょっとだけ上げてもらえませんか?</t>
+          <t xml:space="preserve">社長〜、お給料の話なんですけど、ちょっとだけ上げてもらえませんか？</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、私たちの頑張り、たまには褒めてくれてもいいんですよ?</t>
+          <t xml:space="preserve">社長〜、私たちの頑張り、たまには褒めてくれてもいいんですよ？</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、ちゃんと聞いてくれてた! 嬉しいです、ありがとうございます〜。</t>
+          <t xml:space="preserve">わ、ちゃんと聞いてくれてた！ 嬉しいです、ありがとうございます〜。</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった、社長ありがとう! メイン張りますね!</t>
+          <t xml:space="preserve">やった、社長ありがとう！ メイン張りますね！</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっ、ホントに上げてくれるんですか? やった〜! みんなに自慢しちゃう。</t>
+          <t xml:space="preserve">えっ、ホントに上げてくれるんですか？ やった〜！ みんなに自慢しちゃう。</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ、お金の話そらされた? でもまあ、ありがとうございます〜。</t>
+          <t xml:space="preserve">あれ、お金の話そらされた？ でもまあ、ありがとうございます〜。</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ホント!? やった、社長に褒められちゃった〜!</t>
+          <t xml:space="preserve">ホント！？ やった、社長に褒められちゃった〜！</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、そんなに気にしてました? ごめんなさ〜い、次は誘いますって。</t>
+          <t xml:space="preserve">え、そんなに気にしてました？ ごめんなさ〜い、次は誘いますって。</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった〜、社長わかってる〜! 引き続き暴れまーす。</t>
+          <t xml:space="preserve">やった〜、社長わかってる〜！ 引き続き暴れまーす。</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、ばれてました? すみませ〜ん、明日から出ますって。</t>
+          <t xml:space="preserve">あ、ばれてました？ すみませ〜ん、明日から出ますって。</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、見逃してくれるんですか〜? 助かります〜。</t>
+          <t xml:space="preserve">お、見逃してくれるんですか〜？ 助かります〜。</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ、バレてた? じゃ、お言葉に甘えて休みまーす。</t>
+          <t xml:space="preserve">えへへ、バレてた？ じゃ、お言葉に甘えて休みまーす。</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、メンバーケアですか? 助かりますね〜。</t>
+          <t xml:space="preserve">お、メンバーケアですか？ 助かりますね〜。</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、続けていいんですね〜! やった〜。</t>
+          <t xml:space="preserve">お、続けていいんですね〜！ やった〜。</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ、私じゃなくて子たち優先? まあ、ありがたいですけど〜。</t>
+          <t xml:space="preserve">あれ、私じゃなくて子たち優先？ まあ、ありがたいですけど〜。</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、もう何で揉めてたんだっけ、あたしたち。</t>
+          <t xml:space="preserve">あはは、もう何で揉めてたんだっけ、私たち。</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしも嫌なんだけど、組のみんなが黙ってないから</t>
+          <t xml:space="preserve">私も嫌なんだけど、組のみんなが黙ってないから</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">とりあえず1つ、もらった</t>
+          <t xml:space="preserve">とりあえず一つ、もらった</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー、勝っちゃったか。じゃ、頑張りますわ</t>
+          <t xml:space="preserve">あー、勝っちゃったか。じゃ、やってみるね</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おう、来るかい。じゃあ行こう</t>
+          <t xml:space="preserve">お、来るんだ。じゃあ行こっか</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.standard.easygoing[1]</t>
+          <t xml:space="preserve">autumnWarChampion.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8140,14 +8140,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すっごく楽しかった！ 終わった瞬間「もう1回！」って思ったもん</t>
+          <t xml:space="preserve">団体のみんなが強すぎて、頼もしかったですね！</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.standard.easygoing[2]</t>
+          <t xml:space="preserve">bestMatch.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8172,14 +8172,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合中ずっとニヤニヤしてたかも。だって最高なんだもん！</t>
+          <t xml:space="preserve">すっごく楽しかった！ 終わった瞬間「もう1回！」って思ったもん</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.standard.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.easygoing[1]</t>
+          <t xml:space="preserve">bestMatch.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8204,14 +8204,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンって肩書き、なんかくすぐったいけど最高だね！</t>
+          <t xml:space="preserve">試合中ずっとニヤニヤしてたかも。だって最高なんだもん！</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.standard.easygoing[1]</t>
+          <t xml:space="preserve">champion.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8236,14 +8236,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー楽しかった！ 全部ひっくるめて、最高の人生！ ありがとね！</t>
+          <t xml:space="preserve">チャンピオンって肩書き、なんかくすぐったいけど最高だね！</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.standard.easygoing[2]</t>
+          <t xml:space="preserve">hallOfFame.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8268,14 +8268,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">プロレスに出会えてよかった！ 毎日が冒険みたいだったよ！</t>
+          <t xml:space="preserve">いやー楽しかった！ 全部ひっくるめて、最高の人生！ ありがとね！</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.standard.easygoing[1]</t>
+          <t xml:space="preserve">hallOfFame.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8300,14 +8300,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わーい！ いっぱい出てよかったー！</t>
+          <t xml:space="preserve">プロレスに出会えてよかった！ 毎日が冒険みたいだったよ！</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.standard.easygoing[2]</t>
+          <t xml:space="preserve">mediaAward.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8332,14 +8332,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか気づいたらいっぱいお仕事してました！</t>
+          <t xml:space="preserve">わーい！ いっぱい出てよかったー！</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.standard.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.standard.easygoing[1]</t>
+          <t xml:space="preserve">mediaAward.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8364,14 +8364,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP！ 人生で一番カッコいい三文字もらっちゃった！</t>
+          <t xml:space="preserve">なんか気づいたらいっぱいお仕事してました！</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.standard.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.standard.easygoing[2]</t>
+          <t xml:space="preserve">mvp.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8396,14 +8396,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやーこの一年楽しかったなー。楽しんでたらMVPになってた！</t>
+          <t xml:space="preserve">MVP！ 人生で一番カッコいい三文字もらっちゃった！</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.standard.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.standard.easygoing[1]</t>
+          <t xml:space="preserve">mvp.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8428,14 +8428,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うそでしょ！ 今年一番びっくりしたの、この瞬間かも！</t>
+          <t xml:space="preserve">いやーこの一年楽しかったなー。楽しんでたらMVPになってた！</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.standard.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.standard.easygoing[2]</t>
+          <t xml:space="preserve">rookie.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8460,14 +8460,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー楽しかった！ ここまで来れたの、運がよかっただけかも！</t>
+          <t xml:space="preserve">うそでしょ！ 今年一番びっくりしたの、この瞬間かも！</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[1]</t>
+          <t xml:space="preserve">rookie.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8492,14 +8492,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、ドーム来ちゃいましたねぇ</t>
+          <t xml:space="preserve">いやー楽しかった！ ここまで来れたの、運がよかっただけかも！</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[2]</t>
+          <t xml:space="preserve">springTagChampion.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8524,14 +8524,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだかんだ、楽しみですよ</t>
+          <t xml:space="preserve">いやあ、相棒と組むと楽しいことばっかりですね！</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.easygoing[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[3]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8556,14 +8556,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、いつも通りやりますかー</t>
+          <t xml:space="preserve">いやー、ドーム来ちゃいましたねぇ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8573,12 +8573,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[1]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8588,14 +8588,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うわー、満員だって! びっくりしちゃった</t>
+          <t xml:space="preserve">なんだかんだ、楽しみですよ</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[2]</t>
+          <t xml:space="preserve">standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8620,14 +8620,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりましたねー、本当に嬉しいです</t>
+          <t xml:space="preserve">まぁ、いつも通りやりますかー</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.easygoing[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[3]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8652,14 +8652,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか、胸がじーんとしてます</t>
+          <t xml:space="preserve">うわー、満員だって！ びっくりしちゃった</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8669,29 +8669,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.standard.easygoing[1]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか今日、急にいろいろ掴めた気がする！</t>
+          <t xml:space="preserve">やりましたねー、本当に嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.easygoing[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8701,29 +8701,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.standard.easygoing[2]</t>
+          <t xml:space="preserve">standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よく分かんないけど、急に噛み合ってきた！</t>
+          <t xml:space="preserve">なんか、胸がじーんとしてます</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.standard.easygoing[1]</t>
+          <t xml:space="preserve">N1.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8748,14 +8748,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と一緒だと超楽しい！最高のパートナーだよ！</t>
+          <t xml:space="preserve">なんか今日、急にいろいろ掴めた気がする！</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.standard.easygoing[1]</t>
+          <t xml:space="preserve">N1.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8780,14 +8780,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー、ちょっと疲れちゃったかも。少し休めば平気！</t>
+          <t xml:space="preserve">よく分かんないけど、急に噛み合ってきた！</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.standard.easygoing[1]</t>
+          <t xml:space="preserve">N2.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8812,14 +8812,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの皆さんが喜んでくれるのが一番嬉しい！</t>
+          <t xml:space="preserve">あの人と一緒だと超楽しい！最高のパートナーだよ！</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.easygoing[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.standard.easygoing[2]</t>
+          <t xml:space="preserve">N3.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8844,14 +8844,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっとみんなを楽しませたい！</t>
+          <t xml:space="preserve">あー、ちょっと疲れちゃったかも。少し休めば平気！</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.standard.easygoing[1]</t>
+          <t xml:space="preserve">N4.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8876,14 +8876,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは…もう、いいかなって。ちょっと考えさせて</t>
+          <t xml:space="preserve">ファンの皆さんが喜んでくれるのが一番嬉しい！</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.standard.easygoing[1]</t>
+          <t xml:space="preserve">N4.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8908,14 +8908,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは…いや、ちょっとね。大丈夫、大丈夫</t>
+          <t xml:space="preserve">もっとみんなを楽しませたい！</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8925,29 +8925,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.standard.easygoing[1]</t>
+          <t xml:space="preserve">N5_low.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは……えっと、これは……うん……</t>
+          <t xml:space="preserve">あはは…もう、いいかなって。ちょっと考えさせて</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8957,29 +8957,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.standard.easygoing[1]</t>
+          <t xml:space="preserve">N5_warning.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっと…ありがと…？</t>
+          <t xml:space="preserve">あはは…いや、ちょっとね。大丈夫、大丈夫</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.easygoing[1]</t>
+          <t xml:space="preserve">bonus_insult.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -9004,14 +9004,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった！ありがとうございます！</t>
+          <t xml:space="preserve">あはは……えっと、これは……うん……</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.easygoing[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.easygoing[2]</t>
+          <t xml:space="preserve">bonus_repeat.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -9036,14 +9036,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おごってもらっちゃおうかな！</t>
+          <t xml:space="preserve">えっと…ありがと…？</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.standard.easygoing[1]</t>
+          <t xml:space="preserve">bonus.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9068,14 +9068,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うおー！！合宿だ！楽しみ！</t>
+          <t xml:space="preserve">やった！ありがとうございます！</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.easygoing[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.standard.easygoing[2]</t>
+          <t xml:space="preserve">bonus.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9100,14 +9100,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">夜は枕投げだ！…嘘です、練習します</t>
+          <t xml:space="preserve">おごってもらっちゃおうかな！</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.standard.easygoing[1]</t>
+          <t xml:space="preserve">camp.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9132,14 +9132,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ…見てくれてたんだ。もうちょっと頑張ろうかな！</t>
+          <t xml:space="preserve">うおー！！合宿だ！楽しみ！</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.standard.easygoing[1]</t>
+          <t xml:space="preserve">camp.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9164,14 +9164,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うわー、しんみりした！でも元気出た！やってやる！</t>
+          <t xml:space="preserve">夜は枕投げだ！…嘘です、練習します</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.easygoing[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.standard.easygoing[2]</t>
+          <t xml:space="preserve">encourage_high_trust.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9196,14 +9196,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よし！やってやる！</t>
+          <t xml:space="preserve">えへへ…見てくれてたんだ。もうちょっと頑張ろうかな！</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.standard.easygoing[1]</t>
+          <t xml:space="preserve">encourage.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9228,14 +9228,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まあ、決まったなら仕方ないですね</t>
+          <t xml:space="preserve">うわー、しんみりした！でも元気出た！やってやる！</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.easygoing[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.standard.easygoing[2]</t>
+          <t xml:space="preserve">encourage.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9260,14 +9260,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あーあ。楽しかったんですけどね</t>
+          <t xml:space="preserve">よし！やってやる！</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.standard.easygoing[1]</t>
+          <t xml:space="preserve">faction_decree.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9292,14 +9292,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ！？ ファンのみんな見てる〜？</t>
+          <t xml:space="preserve">……まあ、決まったなら仕方ないですね</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.standard.easygoing[1]</t>
+          <t xml:space="preserve">faction_decree.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9324,14 +9324,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">カンパーイ！！ 今日は無礼講だ〜！</t>
+          <t xml:space="preserve">あーあ。楽しかったんですけどね</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.easygoing[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.standard.easygoing[2]</t>
+          <t xml:space="preserve">media.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9356,14 +9356,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一軒行きましょうよ〜！</t>
+          <t xml:space="preserve">テレビ！？ ファンのみんな見てる〜？</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.standard.easygoing[1]</t>
+          <t xml:space="preserve">party.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9388,14 +9388,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった！バカンスだ！でも戻ったら本気出します！</t>
+          <t xml:space="preserve">カンパーイ！！ 今日は無礼講だ〜！</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.standard.easygoing[1]</t>
+          <t xml:space="preserve">party.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9420,14 +9420,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うわ、専門医まで…！ 早く戻りますね〜！</t>
+          <t xml:space="preserve">もう一軒行きましょうよ〜！</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.standard.easygoing[1]</t>
+          <t xml:space="preserve">refresh_leave.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9452,14 +9452,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マンツーマン！？ めちゃくちゃ贅沢じゃないですか！</t>
+          <t xml:space="preserve">やった！バカンスだ！でも戻ったら本気出します！</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9469,12 +9469,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.standard.easygoing[1]</t>
+          <t xml:space="preserve">special_treatment.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9484,14 +9484,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンのみなさんに、もっと近くで私を見てもらいたい！</t>
+          <t xml:space="preserve">うわ、専門医まで…！ 早く戻りますね〜！</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.easygoing[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.standard.easygoing[2]</t>
+          <t xml:space="preserve">trainer.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9516,14 +9516,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ！？ やった！出たい！</t>
+          <t xml:space="preserve">マンツーマン！？ めちゃくちゃ贅沢じゃないですか！</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.standard.easygoing[1]</t>
+          <t xml:space="preserve">E1.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9548,14 +9548,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジで！？ 他の団体が私を欲しいって！？ ちょっと嬉しいかも…</t>
+          <t xml:space="preserve">ファンのみなさんに、もっと近くで私を見てもらいたい！</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.standard.easygoing[1]</t>
+          <t xml:space="preserve">E1.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9580,14 +9580,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは…今日はちょっとサボりまーす…</t>
+          <t xml:space="preserve">テレビ！？ やった！出たい！</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.easygoing[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.standard.easygoing[2]</t>
+          <t xml:space="preserve">E6.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9612,14 +9612,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習ねぇ…うーん、今日はパスで</t>
+          <t xml:space="preserve">マジで！？ 他の団体が私を欲しいって！？ ちょっと嬉しいかも…</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.standard.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.standard.easygoing[1]</t>
+          <t xml:space="preserve">S_boycott.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9644,14 +9644,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（いつもの笑顔が消え、「ちょっとさぁ…」と珍しく愚痴をこぼしている）</t>
+          <t xml:space="preserve">あはは…今日はちょっとサボりまーす…</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.standard.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.standard.easygoing[1]</t>
+          <t xml:space="preserve">S_boycott.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9676,14 +9676,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「最近ちょっと考えることがあってー」と珍しく真面目な投稿）</t>
+          <t xml:space="preserve">練習ねぇ…うーん、今日はパスで</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.standard.easygoing[1]</t>
+          <t xml:space="preserve">S_grumble.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9708,14 +9708,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえねえ、タイトルマッチ組んでよ！</t>
+          <t xml:space="preserve">（いつもの笑顔が消え、「ちょっとさぁ…」と珍しく愚痴をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.easygoing[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.standard.easygoing[2]</t>
+          <t xml:space="preserve">S_sns.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9740,14 +9740,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト欲しいなー。挑戦させてくれない？</t>
+          <t xml:space="preserve">（SNSに「最近ちょっと考えることがあってー」と珍しく真面目な投稿）</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.standard.easygoing[1]</t>
+          <t xml:space="preserve">S1.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9772,14 +9772,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人との試合組んでよ！決着つけたいんだ！</t>
+          <t xml:space="preserve">ねえねえ、タイトルマッチ組んでよ！</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.standard.easygoing[1]</t>
+          <t xml:space="preserve">S1.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9804,14 +9804,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう限界！ちょっと休まないとマジでやばい！</t>
+          <t xml:space="preserve">ベルト欲しいなー。挑戦させてくれない？</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.standard.easygoing[1]</t>
+          <t xml:space="preserve">S2.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9836,14 +9836,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっちゃけ不満です！ちゃんと話し合いましょう！</t>
+          <t xml:space="preserve">あの人との試合組んでよ！決着つけたいんだ！</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.standard.easygoing[1]</t>
+          <t xml:space="preserve">S3.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9868,14 +9868,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは…いや、なんでも…（笑っているが目が笑っていない）</t>
+          <t xml:space="preserve">もう限界！ちょっと休まないとマジでやばい！</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.standard.easygoing[1]</t>
+          <t xml:space="preserve">S4_direct.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9900,14 +9900,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓したい！もっと強くなりたいんだ！</t>
+          <t xml:space="preserve">ぶっちゃけ不満です！ちゃんと話し合いましょう！</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.standard.easygoing[1]</t>
+          <t xml:space="preserve">S4_silent.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9932,14 +9932,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の面倒見させてよ！楽しそうだし！</t>
+          <t xml:space="preserve">あはは…いや、なんでも…（笑っているが目が笑っていない）</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.standard.easygoing[1]</t>
+          <t xml:space="preserve">S5.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9964,14 +9964,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったー!カメラの前で何しよっかな!</t>
+          <t xml:space="preserve">特訓したい！もっと強くなりたいんだ！</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.recommend.standard.easygoing[1]</t>
+          <t xml:space="preserve">S6.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9996,14 +9996,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えー!? わたしでいいの? やったー!</t>
+          <t xml:space="preserve">後輩の面倒見させてよ！楽しそうだし！</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.standard.easygoing[1]</t>
+          <t xml:space="preserve">E1.accept.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -10028,14 +10028,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いてて…やっちゃいました。でも根性で治します！</t>
+          <t xml:space="preserve">やったー！カメラの前で何しよっかな！</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.standard.easygoing[1]</t>
+          <t xml:space="preserve">E1.recommend.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10060,14 +10060,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつとはもう無理！顔も見たくない！</t>
+          <t xml:space="preserve">えー！？ 私でいいの？ やったー！</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.standard.easygoing[1]</t>
+          <t xml:space="preserve">B1.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10092,14 +10092,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">売られたケンカは買うよ！来いよ！</t>
+          <t xml:space="preserve">いてて…やっちゃいました。でも根性で治します！</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.standard.easygoing[1]</t>
+          <t xml:space="preserve">B2_fighter1.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10124,14 +10124,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コラボ！？ 商品もらえたりする？♪</t>
+          <t xml:space="preserve">あいつとはもう無理！顔も見たくない！</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.standard.easygoing[2]</t>
+          <t xml:space="preserve">B2_fighter2.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10156,14 +10156,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どんな商品になるんだろ〜楽しみ♪</t>
+          <t xml:space="preserve">売られたケンカは買うよ！来いよ！</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.standard.easygoing[1]</t>
+          <t xml:space="preserve">B4_brand.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10188,14 +10188,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CM！？ 私ってもしかして売れっ子？♪</t>
+          <t xml:space="preserve">コラボ！？ 商品もらえたりする？♪</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.standard.easygoing[2]</t>
+          <t xml:space="preserve">B4_brand.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10220,14 +10220,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どんなCMになるんだろ〜楽しみ♪</t>
+          <t xml:space="preserve">どんな商品になるんだろ〜楽しみ♪</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.standard.easygoing[1]</t>
+          <t xml:space="preserve">B4_cm.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10252,14 +10252,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンのみんなに会えるの！ テンション上がる♪</t>
+          <t xml:space="preserve">CM！？ 私ってもしかして売れっ子？♪</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.standard.easygoing[2]</t>
+          <t xml:space="preserve">B4_cm.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10284,14 +10284,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなの笑顔が見れるかな♪</t>
+          <t xml:space="preserve">どんなCMになるんだろ〜楽しみ♪</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.standard.easygoing[1]</t>
+          <t xml:space="preserve">B4_fan.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10316,14 +10316,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファッションショー！ なんかキラキラしてそう♪</t>
+          <t xml:space="preserve">ファンのみんなに会えるの！ テンション上がる♪</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.standard.easygoing[2]</t>
+          <t xml:space="preserve">B4_fan.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10348,14 +10348,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">衣装とかかわいいのかな〜♪</t>
+          <t xml:space="preserve">みんなの笑顔が見れるかな♪</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.standard.easygoing[1]</t>
+          <t xml:space="preserve">B4_fashion.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10380,14 +10380,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビアか〜！ どんな感じになるんだろ♪</t>
+          <t xml:space="preserve">ファッションショー！ なんかキラキラしてそう♪</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.standard.easygoing[2]</t>
+          <t xml:space="preserve">B4_fashion.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10412,14 +10412,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">かわいく撮ってもらえるかな♪</t>
+          <t xml:space="preserve">衣装とかかわいいのかな〜♪</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.standard.easygoing[1]</t>
+          <t xml:space="preserve">B4_gravure.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10444,14 +10444,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティ！ 笑わせにいくよ♪</t>
+          <t xml:space="preserve">グラビアか〜！ どんな感じになるんだろ♪</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.standard.easygoing[2]</t>
+          <t xml:space="preserve">B4_gravure.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10476,14 +10476,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビって楽しそう！ 全力でいく♪</t>
+          <t xml:space="preserve">かわいく撮ってもらえるかな♪</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.standard.easygoing[1]</t>
+          <t xml:space="preserve">B4_variety.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10508,14 +10508,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">マジで！？ テレビに出れるの！？ やったー！</t>
+          <t xml:space="preserve">バラエティ！ 笑わせにいくよ♪</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.standard.easygoing[2]</t>
+          <t xml:space="preserve">B4_variety.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10540,14 +10540,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの皆さんにもっと近い姿を見せられるね！</t>
+          <t xml:space="preserve">テレビって楽しそう！ 全力でいく♪</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10557,29 +10557,29 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[1]</t>
+          <t xml:space="preserve">B4.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ、一緒に楽しくやりましょうよ！</t>
+          <t xml:space="preserve">マジで！？ テレビに出れるの！？ やったー！</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10589,29 +10589,29 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[2]</t>
+          <t xml:space="preserve">B4.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈なプロレスはしないって約束するよ！</t>
+          <t xml:space="preserve">ファンの皆さんにもっと近い姿を見せられるね！</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
@@ -10636,14 +10636,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、やっとだね。よろしく〜</t>
+          <t xml:space="preserve">えへへ、一緒に楽しくやりましょうよ！</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
@@ -10668,14 +10668,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ、よろしくお願いしまーす</t>
+          <t xml:space="preserve">退屈なプロレスはしないって約束するよ！</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.easygoing[3]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[3]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10700,14 +10700,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと楽しくやりたいな。よろしくね</t>
+          <t xml:space="preserve">いやー、やっとだね。よろしく〜</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[1]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10732,14 +10732,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっほー！新天地だ！暴れまくるよ！</t>
+          <t xml:space="preserve">えへへ、よろしくお願いしまーす</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[2]</t>
+          <t xml:space="preserve">standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10764,14 +10764,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここなら好き放題やれそう！楽しみ！</t>
+          <t xml:space="preserve">みんなと楽しくやりたいな。よろしくね</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
@@ -10796,14 +10796,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わーい！今日から仲間だ！よろしく！</t>
+          <t xml:space="preserve">やっほー！新天地だ！暴れまくるよ！</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
@@ -10828,14 +10828,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで楽しくやりましょー！</t>
+          <t xml:space="preserve">ここなら好き放題やれそう！楽しみ！</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
@@ -10860,14 +10860,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっちゃったー。ちょっと休むね</t>
+          <t xml:space="preserve">わーい！今日から仲間だ！よろしく！</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
@@ -10892,14 +10892,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ…ごめん、ちょっと休むよ</t>
+          <t xml:space="preserve">みんなで楽しくやりましょー！</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.easygoing[3]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[3]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10924,14 +10924,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、こういう時もあるよね。すぐ戻るから</t>
+          <t xml:space="preserve">やっちゃったー。ちょっと休むね</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.standard.easygoing[1]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10956,14 +10956,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はぁ……また？ もう終わった話でしょ、これ</t>
+          <t xml:space="preserve">えへへ…ごめん、ちょっと休むよ</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10973,12 +10973,12 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.standard.easygoing[2]</t>
+          <t xml:space="preserve">standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10988,14 +10988,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っても軽くならないもんだね。……不思議</t>
+          <t xml:space="preserve">まぁ、こういう時もあるよね。すぐ戻るから</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.standard.easygoing[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -11020,14 +11020,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんな綺麗に忘れてるね。……あたしは忘れないけど</t>
+          <t xml:space="preserve">はぁ……また？ もう終わった話でしょ、これ</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.standard.easygoing[2]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -11052,14 +11052,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いつまでやるんだろうね、これ。……やめられないけど</t>
+          <t xml:space="preserve">勝っても軽くならないもんだね。……不思議</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.standard.easygoing[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -11084,14 +11084,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ、一緒に楽しくやりましょうよ！</t>
+          <t xml:space="preserve">みんな綺麗に忘れてるね。……私は忘れないけど</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.standard.easygoing[2]</t>
+          <t xml:space="preserve">bitterPrematch.behind.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11116,14 +11116,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈なプロレスはしないって約束するよ！</t>
+          <t xml:space="preserve">いつまでやるんだろうね、これ。……やめられないけど</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.easygoing[1]</t>
+          <t xml:space="preserve">draftInterest.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11148,14 +11148,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、やっとだね。よろしく〜</t>
+          <t xml:space="preserve">えへへ、一緒に楽しくやりましょうよ！</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.easygoing[2]</t>
+          <t xml:space="preserve">draftInterest.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11180,14 +11180,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ、よろしくお願いしまーす</t>
+          <t xml:space="preserve">退屈なプロレスはしないって約束するよ！</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.easygoing[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.easygoing[3]</t>
+          <t xml:space="preserve">draftJoin.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11212,14 +11212,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと楽しくやりたいな。よろしくね</t>
+          <t xml:space="preserve">いやー、やっとだね。よろしく〜</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.easygoing[1]</t>
+          <t xml:space="preserve">draftJoin.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11244,14 +11244,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーも気楽だったけどねー。ここらで腰を据えるか</t>
+          <t xml:space="preserve">えへへ、よろしくお願いしまーす</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.easygoing[2]</t>
+          <t xml:space="preserve">draftJoin.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11276,14 +11276,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声かかんなくてさー。拾ってくれて助かったよ</t>
+          <t xml:space="preserve">みんなと楽しくやりたいな。よろしくね</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.standard.easygoing[1]</t>
+          <t xml:space="preserve">faGreeting.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11308,14 +11308,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっほー！新天地だ！暴れまくるよ！</t>
+          <t xml:space="preserve">フリーも気楽だったけどねー。ここらで腰を据えるか</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.standard.easygoing[2]</t>
+          <t xml:space="preserve">faGreeting.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11340,14 +11340,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここなら好き放題やれそう！楽しみ！</t>
+          <t xml:space="preserve">しばらく声かかんなくてさー。呼んでくれて嬉しいよ</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.standard.easygoing[1]</t>
+          <t xml:space="preserve">faSigning.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11372,14 +11372,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わーい！今日から仲間だ！よろしく！</t>
+          <t xml:space="preserve">やっほー！新天地だ！暴れまくるよ！</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11394,7 +11394,7 @@
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.standard.easygoing[2]</t>
+          <t xml:space="preserve">faSigning.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11404,14 +11404,14 @@
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで楽しくやりましょー！</t>
+          <t xml:space="preserve">ここなら好き放題やれそう！楽しみ！</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.standard.easygoing[1]</t>
+          <t xml:space="preserve">faWelcome.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11436,14 +11436,14 @@
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか今日、体が軽いんだよねー。いけるいける</t>
+          <t xml:space="preserve">わーい！今日から仲間だ！よろしく！</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.standard.easygoing[1]</t>
+          <t xml:space="preserve">faWelcome.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11468,14 +11468,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー、体が重い。今日は何やっても身にならないねー</t>
+          <t xml:space="preserve">みんなで楽しくやりましょー！</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.standard.easygoing[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11500,14 +11500,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">んー、なんか乗り切らないなー。動けてはいるけど</t>
+          <t xml:space="preserve">なんか今日、体が軽いんだよねー。いけるいける</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.easygoing[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11532,14 +11532,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっちゃったー。ちょっと休むね</t>
+          <t xml:space="preserve">あー、体が重い。今日は何やっても身にならないねー</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.easygoing[2]</t>
+          <t xml:space="preserve">heatSelf.warm.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11564,14 +11564,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ…ごめん、ちょっと休むよ</t>
+          <t xml:space="preserve">んー、なんか乗り切らないなー。動けてはいるけど</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.easygoing[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.easygoing[3]</t>
+          <t xml:space="preserve">injury.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11596,14 +11596,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、こういう時もあるよね。すぐ戻るから</t>
+          <t xml:space="preserve">やっちゃったー。ちょっと休むね</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.easygoing[1]</t>
+          <t xml:space="preserve">injury.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11628,14 +11628,14 @@
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、こういう時もあるよね。みんな、元気でね！</t>
+          <t xml:space="preserve">えへへ…ごめん、ちょっと休むよ</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.easygoing[2]</t>
+          <t xml:space="preserve">injury.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11660,14 +11660,14 @@
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ、ここでの日々は楽しかったよ。ありがとう</t>
+          <t xml:space="preserve">まぁ、こういう時もあるよね。すぐ戻るから</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.easygoing[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.easygoing[3]</t>
+          <t xml:space="preserve">release.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11692,14 +11692,14 @@
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">縁がなかったってことだね。まぁ、お元気で〜</t>
+          <t xml:space="preserve">まぁ、こういう時もあるよね。みんな、元気でね！</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.standard.easygoing[1]</t>
+          <t xml:space="preserve">release.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11724,14 +11724,14 @@
       </c>
       <c r="F354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おじゃましまーす！短い間だけど暴れるよー！</t>
+          <t xml:space="preserve">えへへ、ここでの日々は楽しかったよ。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.standard.easygoing[2]</t>
+          <t xml:space="preserve">release.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11756,14 +11756,14 @@
       </c>
       <c r="F355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一時的だからこそ思い切り好き放題やるね！</t>
+          <t xml:space="preserve">縁がなかったってことだね。まぁ、お元気で〜</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.easygoing[1]</t>
+          <t xml:space="preserve">rentalGreeting.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E356" t="inlineStr" s="2">
@@ -11788,14 +11788,14 @@
       </c>
       <c r="F356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よく見つけたねー。掘り出し物だよ、あたし</t>
+          <t xml:space="preserve">おじゃましまーす！短い間だけど暴れるよー！</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="D357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.easygoing[2]</t>
+          <t xml:space="preserve">rentalGreeting.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11820,14 +11820,14 @@
       </c>
       <c r="F357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょうど暴れる場所探してたんだ。よろしくね</t>
+          <t xml:space="preserve">一時的だからこそ思い切り好き放題やるね！</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.standard.easygoing[1]</t>
+          <t xml:space="preserve">scoutGreeting.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11852,14 +11852,14 @@
       </c>
       <c r="F358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けちゃったけど…次はもっといい試合するから！</t>
+          <t xml:space="preserve">よく見つけたねー。掘り出し物だよ、私</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.standard.easygoing[2]</t>
+          <t xml:space="preserve">scoutGreeting.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11884,14 +11884,14 @@
       </c>
       <c r="F359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいけど、下向いてたら応援してくれる人に失礼だもんね</t>
+          <t xml:space="preserve">ちょうど暴れる場所探してたんだ。よろしくね</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.standard.easygoing[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11916,14 +11916,14 @@
       </c>
       <c r="F360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンは私！また守り切っちゃいました！</t>
+          <t xml:space="preserve">今日は負けちゃったけど…次はもっといい試合するから！</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="D361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.standard.easygoing[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11948,14 +11948,14 @@
       </c>
       <c r="F361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合だった！また挑戦してきてね！</t>
+          <t xml:space="preserve">悔しいけど、下向いてたら応援してくれる人に失礼だもんね</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.standard.easygoing[1]</t>
+          <t xml:space="preserve">titleDefense.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E362" t="inlineStr" s="2">
@@ -11980,14 +11980,14 @@
       </c>
       <c r="F362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃった…でもファンが応援してくれる限り、立ち上がるよ</t>
+          <t xml:space="preserve">チャンピオンは私！また守り切っちゃいました！</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.standard.easygoing[2]</t>
+          <t xml:space="preserve">titleDefense.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -12012,14 +12012,14 @@
       </c>
       <c r="F363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトがない自分なんて想像できなかった。でも、私は私だから</t>
+          <t xml:space="preserve">いい試合だった！また挑戦してきてね！</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.standard.easygoing[1]</t>
+          <t xml:space="preserve">titleLoss.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -12044,14 +12044,14 @@
       </c>
       <c r="F364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新チャンピオン誕生！みんな、これからもっと盛り上がるよ！</t>
+          <t xml:space="preserve">負けちゃった…でもファンが応援してくれる限り、立ち上がるよ</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.standard.easygoing[2]</t>
+          <t xml:space="preserve">titleLoss.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -12076,14 +12076,14 @@
       </c>
       <c r="F365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト獲っちゃった！最高！</t>
+          <t xml:space="preserve">…ベルトがない自分なんて想像できなかった。でも、私は私だから</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -12093,12 +12093,12 @@
       </c>
       <c r="C366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[1]</t>
+          <t xml:space="preserve">titleWin.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
@@ -12108,14 +12108,14 @@
       </c>
       <c r="F366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、こういう時もあるよね。みんな、元気でね！</t>
+          <t xml:space="preserve">新チャンピオン誕生！みんな、これからもっと盛り上がるよ！</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -12125,12 +12125,12 @@
       </c>
       <c r="C367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[2]</t>
+          <t xml:space="preserve">titleWin.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -12140,14 +12140,14 @@
       </c>
       <c r="F367" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ、ここでの日々は楽しかったよ。ありがとう</t>
+          <t xml:space="preserve">ベルト獲っちゃった！最高！</t>
         </is>
       </c>
     </row>
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.easygoing[3]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -12162,7 +12162,7 @@
       </c>
       <c r="D368" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[3]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -12172,14 +12172,14 @@
       </c>
       <c r="F368" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">縁がなかったってことだね。まぁ、お元気で〜</t>
+          <t xml:space="preserve">まぁ、こういう時もあるよね。みんな、元気でね！</t>
         </is>
       </c>
     </row>
     <row r="369" ht="40" customHeight="1">
       <c r="A369" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="C369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D369" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[1]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E369" t="inlineStr" s="2">
@@ -12204,14 +12204,14 @@
       </c>
       <c r="F369" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おじゃましまーす！短い間だけど暴れるよー！</t>
+          <t xml:space="preserve">えへへ、ここでの日々は楽しかったよ。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="370" ht="40" customHeight="1">
       <c r="A370" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -12221,12 +12221,12 @@
       </c>
       <c r="C370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D370" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[2]</t>
+          <t xml:space="preserve">standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E370" t="inlineStr" s="2">
@@ -12236,14 +12236,14 @@
       </c>
       <c r="F370" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一時的だからこそ思い切り好き放題やるね！</t>
+          <t xml:space="preserve">縁がなかったってことだね。まぁ、お元気で〜</t>
         </is>
       </c>
     </row>
     <row r="371" ht="40" customHeight="1">
       <c r="A371" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="C371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D371" t="inlineStr" s="12">
@@ -12268,14 +12268,14 @@
       </c>
       <c r="F371" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けちゃったけど…次はもっといい試合するから！</t>
+          <t xml:space="preserve">おじゃましまーす！短い間だけど暴れるよー！</t>
         </is>
       </c>
     </row>
     <row r="372" ht="40" customHeight="1">
       <c r="A372" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D372" t="inlineStr" s="12">
@@ -12300,14 +12300,14 @@
       </c>
       <c r="F372" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいけど、下向いてたら応援してくれる人に失礼だもんね</t>
+          <t xml:space="preserve">一時的だからこそ思い切り好き放題やるね！</t>
         </is>
       </c>
     </row>
     <row r="373" ht="40" customHeight="1">
       <c r="A373" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="C373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D373" t="inlineStr" s="12">
@@ -12332,14 +12332,14 @@
       </c>
       <c r="F373" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンは私！また守り切っちゃいました！</t>
+          <t xml:space="preserve">今日は負けちゃったけど…次はもっといい試合するから！</t>
         </is>
       </c>
     </row>
     <row r="374" ht="40" customHeight="1">
       <c r="A374" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="C374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D374" t="inlineStr" s="12">
@@ -12364,14 +12364,14 @@
       </c>
       <c r="F374" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合だった！また挑戦してきてね！</t>
+          <t xml:space="preserve">悔しいけど、下向いてたら応援してくれる人に失礼だもんね</t>
         </is>
       </c>
     </row>
     <row r="375" ht="40" customHeight="1">
       <c r="A375" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="C375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D375" t="inlineStr" s="12">
@@ -12396,14 +12396,14 @@
       </c>
       <c r="F375" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃった…でもファンが応援してくれる限り、立ち上がるよ</t>
+          <t xml:space="preserve">チャンピオンは私！また守り切っちゃいました！</t>
         </is>
       </c>
     </row>
     <row r="376" ht="40" customHeight="1">
       <c r="A376" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="C376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D376" t="inlineStr" s="12">
@@ -12428,14 +12428,14 @@
       </c>
       <c r="F376" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトがない自分なんて想像できなかった。でも、私は私だから</t>
+          <t xml:space="preserve">いい試合だった！また挑戦してきてね！</t>
         </is>
       </c>
     </row>
     <row r="377" ht="40" customHeight="1">
       <c r="A377" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="C377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D377" t="inlineStr" s="12">
@@ -12460,14 +12460,14 @@
       </c>
       <c r="F377" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新チャンピオン誕生！みんな、これからもっと盛り上がるよ！</t>
+          <t xml:space="preserve">負けちゃった…でもファンが応援してくれる限り、立ち上がるよ</t>
         </is>
       </c>
     </row>
     <row r="378" ht="40" customHeight="1">
       <c r="A378" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="C378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D378" t="inlineStr" s="12">
@@ -12492,14 +12492,14 @@
       </c>
       <c r="F378" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト獲っちゃった！最高！</t>
+          <t xml:space="preserve">…ベルトがない自分なんて想像できなかった。でも、私は私だから</t>
         </is>
       </c>
     </row>
     <row r="379" ht="40" customHeight="1">
       <c r="A379" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.standard[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
@@ -12509,29 +12509,29 @@
       </c>
       <c r="C379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D379" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.standard[1]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F379" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、ちょっと合わないかもなぁ…</t>
+          <t xml:space="preserve">新チャンピオン誕生！みんな、これからもっと盛り上がるよ！</t>
         </is>
       </c>
     </row>
     <row r="380" ht="40" customHeight="1">
       <c r="A380" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.standard[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
@@ -12541,29 +12541,29 @@
       </c>
       <c r="C380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D380" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.standard[1]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F380" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ〜、最近ちょっと素っ気ないなぁ</t>
+          <t xml:space="preserve">ベルト獲っちゃった！最高！</t>
         </is>
       </c>
     </row>
     <row r="381" ht="40" customHeight="1">
       <c r="A381" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="D381" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.standard[2]</t>
+          <t xml:space="preserve">bond_39_down.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="E381" t="inlineStr" s="2">
@@ -12588,14 +12588,14 @@
       </c>
       <c r="F381" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ん〜なんだろ、微妙に空気変わった？</t>
+          <t xml:space="preserve">う〜ん、ちょっと合わないかもなぁ…</t>
         </is>
       </c>
     </row>
     <row r="382" ht="40" customHeight="1">
       <c r="A382" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -12610,7 +12610,7 @@
       </c>
       <c r="D382" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.standard[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="E382" t="inlineStr" s="2">
@@ -12620,14 +12620,14 @@
       </c>
       <c r="F382" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ノリが合うんだよね〜。一緒にいると楽しいわ</t>
+          <t xml:space="preserve">あれ〜、最近ちょっと素っ気ないなぁ</t>
         </is>
       </c>
     </row>
     <row r="383" ht="40" customHeight="1">
       <c r="A383" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="D383" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.standard[2]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="E383" t="inlineStr" s="2">
@@ -12652,14 +12652,14 @@
       </c>
       <c r="F383" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、一緒にいると時間忘れちゃう</t>
+          <t xml:space="preserve">ん〜なんだろ、微妙に空気変わった？</t>
         </is>
       </c>
     </row>
     <row r="384" ht="40" customHeight="1">
       <c r="A384" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="D384" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.standard[1]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="E384" t="inlineStr" s="2">
@@ -12684,14 +12684,14 @@
       </c>
       <c r="F384" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の相棒だよ〜。ずっと一緒にいたいな</t>
+          <t xml:space="preserve">ノリが合うんだよね〜。一緒にいると楽しいわ</t>
         </is>
       </c>
     </row>
     <row r="385" ht="40" customHeight="1">
       <c r="A385" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="D385" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.standard[2]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="E385" t="inlineStr" s="2">
@@ -12716,14 +12716,14 @@
       </c>
       <c r="F385" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると全部うまくいく気がするんだよね</t>
+          <t xml:space="preserve">あはは、一緒にいると時間忘れちゃう</t>
         </is>
       </c>
     </row>
     <row r="386" ht="40" customHeight="1">
       <c r="A386" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="D386" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.standard[1]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="E386" t="inlineStr" s="2">
@@ -12748,14 +12748,14 @@
       </c>
       <c r="F386" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い関係も一段落かぁ。ちょっと寂しいね</t>
+          <t xml:space="preserve">最高の相棒だよ〜。ずっと一緒にいたいな</t>
         </is>
       </c>
     </row>
     <row r="387" ht="40" customHeight="1">
       <c r="A387" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="D387" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.standard[2]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="E387" t="inlineStr" s="2">
@@ -12780,14 +12780,14 @@
       </c>
       <c r="F387" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ因縁も永遠じゃないよね〜</t>
+          <t xml:space="preserve">一緒にいると全部うまくいく気がするんだよね</t>
         </is>
       </c>
     </row>
     <row r="388" ht="40" customHeight="1">
       <c r="A388" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="D388" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.standard[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="2">
@@ -12812,14 +12812,14 @@
       </c>
       <c r="F388" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい勝負になりそうだね〜。燃えてきた</t>
+          <t xml:space="preserve">熱い関係も一段落かぁ。ちょっと寂しいね</t>
         </is>
       </c>
     </row>
     <row r="389" ht="40" customHeight="1">
       <c r="A389" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="D389" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.standard[2]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="E389" t="inlineStr" s="2">
@@ -12844,14 +12844,14 @@
       </c>
       <c r="F389" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、負けたくないなぁ</t>
+          <t xml:space="preserve">まぁ因縁も永遠じゃないよね〜</t>
         </is>
       </c>
     </row>
     <row r="390" ht="40" customHeight="1">
       <c r="A390" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="D390" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.standard[1]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="E390" t="inlineStr" s="2">
@@ -12876,14 +12876,14 @@
       </c>
       <c r="F390" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本気でやり合いたい相手って、そうはいないよ</t>
+          <t xml:space="preserve">いい勝負になりそうだね〜。燃えてきた</t>
         </is>
       </c>
     </row>
     <row r="391" ht="40" customHeight="1">
       <c r="A391" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="D391" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.standard[2]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="E391" t="inlineStr" s="2">
@@ -12908,14 +12908,14 @@
       </c>
       <c r="F391" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、考えると自然と気合入るわ</t>
+          <t xml:space="preserve">あはは、負けたくないなぁ</t>
         </is>
       </c>
     </row>
     <row r="392" ht="40" customHeight="1">
       <c r="A392" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="D392" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.standard[1]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="E392" t="inlineStr" s="2">
@@ -12940,14 +12940,14 @@
       </c>
       <c r="F392" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この試合が一番楽しい。ずっとこの関係が続けばいいのに</t>
+          <t xml:space="preserve">本気でやり合いたい相手って、そうはいないよ</t>
         </is>
       </c>
     </row>
     <row r="393" ht="40" customHeight="1">
       <c r="A393" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="D393" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.standard[2]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="E393" t="inlineStr" s="2">
@@ -12972,14 +12972,14 @@
       </c>
       <c r="F393" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命のライバルだね〜。最高だよ</t>
+          <t xml:space="preserve">ふふ、考えると自然と気合入るわ</t>
         </is>
       </c>
     </row>
     <row r="394" ht="40" customHeight="1">
       <c r="A394" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="D394" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.standard[1]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="E394" t="inlineStr" s="2">
@@ -13004,14 +13004,14 @@
       </c>
       <c r="F394" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここ最高〜！ みんなとやるの楽しいよ！</t>
+          <t xml:space="preserve">この試合が一番楽しい。ずっとこの関係が続けばいいのに</t>
         </is>
       </c>
     </row>
     <row r="395" ht="40" customHeight="1">
       <c r="A395" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="D395" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.standard[2]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="E395" t="inlineStr" s="2">
@@ -13036,14 +13036,14 @@
       </c>
       <c r="F395" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、すっごく居心地いいんだよね〜</t>
+          <t xml:space="preserve">運命のライバルだね〜。最高だよ</t>
         </is>
       </c>
     </row>
     <row r="396" ht="40" customHeight="1">
       <c r="A396" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="D396" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.standard[1]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="E396" t="inlineStr" s="2">
@@ -13068,14 +13068,14 @@
       </c>
       <c r="F396" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがにこれは…笑えないかも</t>
+          <t xml:space="preserve">ここ最高〜！ みんなとやるの楽しいよ！</t>
         </is>
       </c>
     </row>
     <row r="397" ht="40" customHeight="1">
       <c r="A397" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
@@ -13090,7 +13090,7 @@
       </c>
       <c r="D397" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.standard[2]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="E397" t="inlineStr" s="2">
@@ -13100,14 +13100,14 @@
       </c>
       <c r="F397" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは…って笑ってる場合じゃないよね、これ</t>
+          <t xml:space="preserve">この団体、すっごく居心地いいんだよね〜</t>
         </is>
       </c>
     </row>
     <row r="398" ht="40" customHeight="1">
       <c r="A398" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="D398" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.standard[1]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="E398" t="inlineStr" s="2">
@@ -13132,14 +13132,14 @@
       </c>
       <c r="F398" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、最近ちょっとモヤモヤするなぁ…</t>
+          <t xml:space="preserve">さすがにこれは…笑えないかも</t>
         </is>
       </c>
     </row>
     <row r="399" ht="40" customHeight="1">
       <c r="A399" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="D399" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.standard[2]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="E399" t="inlineStr" s="2">
@@ -13164,14 +13164,14 @@
       </c>
       <c r="F399" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ大丈夫…だよね？ ちょっと不安だけど</t>
+          <t xml:space="preserve">あはは…って笑ってる場合じゃないよね、これ</t>
         </is>
       </c>
     </row>
     <row r="400" ht="40" customHeight="1">
       <c r="A400" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
@@ -13181,12 +13181,12 @@
       </c>
       <c r="C400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D400" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.standard.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.standard[1]</t>
         </is>
       </c>
       <c r="E400" t="inlineStr" s="2">
@@ -13196,14 +13196,14 @@
       </c>
       <c r="F400" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合だったなぁ〜。負けたけど満足かも</t>
+          <t xml:space="preserve">う〜ん、最近ちょっとモヤモヤするなぁ…</t>
         </is>
       </c>
     </row>
     <row r="401" ht="40" customHeight="1">
       <c r="A401" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
@@ -13213,12 +13213,12 @@
       </c>
       <c r="C401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D401" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.standard.easygoing[2]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.standard[2]</t>
         </is>
       </c>
       <c r="E401" t="inlineStr" s="2">
@@ -13228,14 +13228,14 @@
       </c>
       <c r="F401" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手が強かった！ でも楽しかった〜</t>
+          <t xml:space="preserve">まぁ大丈夫…だよね？ ちょっと不安だけど</t>
         </is>
       </c>
     </row>
     <row r="402" ht="40" customHeight="1">
       <c r="A402" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="D402" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E402" t="inlineStr" s="2">
@@ -13260,14 +13260,14 @@
       </c>
       <c r="F402" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高〜〜〜！ こういう試合のためにプロレスやってんだよ！</t>
+          <t xml:space="preserve">いい試合だったなぁ〜。負けたけど満足かも</t>
         </is>
       </c>
     </row>
     <row r="403" ht="40" customHeight="1">
       <c r="A403" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="D403" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.easygoing[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E403" t="inlineStr" s="2">
@@ -13292,14 +13292,14 @@
       </c>
       <c r="F403" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合で勝てるって最高だね〜！</t>
+          <t xml:space="preserve">相手が強かった！ でも楽しかった〜</t>
         </is>
       </c>
     </row>
     <row r="404" ht="40" customHeight="1">
       <c r="A404" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="D404" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E404" t="inlineStr" s="2">
@@ -13324,14 +13324,14 @@
       </c>
       <c r="F404" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あちゃ〜、負けちゃった。次頑張ろ</t>
+          <t xml:space="preserve">最高〜〜〜！ こういう試合のためにプロレスやってんだよ！</t>
         </is>
       </c>
     </row>
     <row r="405" ht="40" customHeight="1">
       <c r="A405" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="D405" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.standard.easygoing[2]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E405" t="inlineStr" s="2">
@@ -13356,14 +13356,14 @@
       </c>
       <c r="F405" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残念〜。でもいい勉強になったかな</t>
+          <t xml:space="preserve">いい試合で勝てるって最高だね〜！</t>
         </is>
       </c>
     </row>
     <row r="406" ht="40" customHeight="1">
       <c r="A406" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="D406" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-01.loss.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E406" t="inlineStr" s="2">
@@ -13388,14 +13388,14 @@
       </c>
       <c r="F406" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった〜勝った〜！ 今日のご褒美何にしよう</t>
+          <t xml:space="preserve">あちゃ〜、負けちゃった。次頑張ろ</t>
         </is>
       </c>
     </row>
     <row r="407" ht="40" customHeight="1">
       <c r="A407" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
@@ -13410,7 +13410,7 @@
       </c>
       <c r="D407" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.easygoing[2]</t>
+          <t xml:space="preserve">GL-01.loss.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E407" t="inlineStr" s="2">
@@ -13420,14 +13420,14 @@
       </c>
       <c r="F407" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝利！ いい一日だね〜</t>
+          <t xml:space="preserve">残念〜。でもいい勉強になったかな</t>
         </is>
       </c>
     </row>
     <row r="408" ht="40" customHeight="1">
       <c r="A408" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="D408" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-01.win.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E408" t="inlineStr" s="2">
@@ -13452,14 +13452,14 @@
       </c>
       <c r="F408" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習たのし〜。いい汗かいてるわ</t>
+          <t xml:space="preserve">やった〜勝った〜！ 今日のご褒美何にしよう</t>
         </is>
       </c>
     </row>
     <row r="409" ht="40" customHeight="1">
       <c r="A409" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="D409" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.easygoing[2]</t>
+          <t xml:space="preserve">GL-01.win.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E409" t="inlineStr" s="2">
@@ -13484,14 +13484,14 @@
       </c>
       <c r="F409" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よーし、今日もがんばるぞ〜っと</t>
+          <t xml:space="preserve">勝利！ いい一日だね〜</t>
         </is>
       </c>
     </row>
     <row r="410" ht="40" customHeight="1">
       <c r="A410" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="D410" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-02.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E410" t="inlineStr" s="2">
@@ -13516,14 +13516,14 @@
       </c>
       <c r="F410" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ〜？ なんかちょっと居心地悪くなった？</t>
+          <t xml:space="preserve">練習たのし〜。いい汗かいてるわ</t>
         </is>
       </c>
     </row>
     <row r="411" ht="40" customHeight="1">
       <c r="A411" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="D411" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-02.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E411" t="inlineStr" s="2">
@@ -13548,14 +13548,14 @@
       </c>
       <c r="F411" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近めっちゃ楽しい〜。ここ大好き！</t>
+          <t xml:space="preserve">よーし、今日もがんばるぞ〜っと</t>
         </is>
       </c>
     </row>
     <row r="412" ht="40" customHeight="1">
       <c r="A412" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="D412" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-03.down.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E412" t="inlineStr" s="2">
@@ -13580,14 +13580,14 @@
       </c>
       <c r="F412" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒だとテンション上がるわ〜</t>
+          <t xml:space="preserve">あれ〜？ なんかちょっと居心地悪くなった？</t>
         </is>
       </c>
     </row>
     <row r="413" ht="40" customHeight="1">
       <c r="A413" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="D413" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-03.up.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E413" t="inlineStr" s="2">
@@ -13612,14 +13612,14 @@
       </c>
       <c r="F413" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気になって仕方ないんだよね〜</t>
+          <t xml:space="preserve">最近めっちゃ楽しい〜。ここ大好き！</t>
         </is>
       </c>
     </row>
     <row r="414" ht="40" customHeight="1">
       <c r="A414" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="D414" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-04.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E414" t="inlineStr" s="2">
@@ -13644,14 +13644,14 @@
       </c>
       <c r="F414" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ今週は仕方ないか〜。でもちょっと寂しいな</t>
+          <t xml:space="preserve">一緒だとテンション上がるわ〜</t>
         </is>
       </c>
     </row>
     <row r="415" ht="40" customHeight="1">
       <c r="A415" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="D415" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.easygoing[2]</t>
+          <t xml:space="preserve">GL-05.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E415" t="inlineStr" s="2">
@@ -13676,14 +13676,14 @@
       </c>
       <c r="F415" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お休みかぁ。まぁたまにはね。…うん、寂しいけど</t>
+          <t xml:space="preserve">気になって仕方ないんだよね〜</t>
         </is>
       </c>
     </row>
     <row r="416" ht="40" customHeight="1">
       <c r="A416" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="D416" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-06.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E416" t="inlineStr" s="2">
@@ -13708,14 +13708,14 @@
       </c>
       <c r="F416" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、体がだるいなぁ。ちょっと休もっかな</t>
+          <t xml:space="preserve">まあ今週は仕方ないか〜。でもちょっと寂しいな</t>
         </is>
       </c>
     </row>
     <row r="417" ht="40" customHeight="1">
       <c r="A417" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B417" t="inlineStr" s="2">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="D417" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-06.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E417" t="inlineStr" s="2">
@@ -13740,14 +13740,14 @@
       </c>
       <c r="F417" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは…笑えない状況だね…さすがに凹むわ</t>
+          <t xml:space="preserve">お休みかぁ。まぁたまにはね。…うん、寂しいけど</t>
         </is>
       </c>
     </row>
     <row r="418" ht="40" customHeight="1">
       <c r="A418" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B418" t="inlineStr" s="2">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="D418" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.easygoing[2]</t>
+          <t xml:space="preserve">GL-07.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E418" t="inlineStr" s="2">
@@ -13772,14 +13772,14 @@
       </c>
       <c r="F418" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、負けが込んでるなぁ…どうしたもんか</t>
+          <t xml:space="preserve">う〜ん、体がだるいなぁ。ちょっと休もっかな</t>
         </is>
       </c>
     </row>
     <row r="419" ht="40" customHeight="1">
       <c r="A419" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B419" t="inlineStr" s="2">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="D419" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-08.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E419" t="inlineStr" s="2">
@@ -13804,14 +13804,14 @@
       </c>
       <c r="F419" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝〜！ ノッてるね〜。この波乗りこなすぞ〜</t>
+          <t xml:space="preserve">あはは…笑えない状況だね…さすがに凹むわ</t>
         </is>
       </c>
     </row>
     <row r="420" ht="40" customHeight="1">
       <c r="A420" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B420" t="inlineStr" s="2">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="D420" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-08.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E420" t="inlineStr" s="2">
@@ -13836,14 +13836,14 @@
       </c>
       <c r="F420" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我かぁ…暇だなぁ。早く治らないかな〜</t>
+          <t xml:space="preserve">う〜ん、負けが込んでるなぁ…どうしたもんか</t>
         </is>
       </c>
     </row>
     <row r="421" ht="40" customHeight="1">
       <c r="A421" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B421" t="inlineStr" s="2">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="D421" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.easygoing[2]</t>
+          <t xml:space="preserve">GL-09.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E421" t="inlineStr" s="2">
@@ -13868,14 +13868,14 @@
       </c>
       <c r="F421" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">じっとしてるの苦手なんだよね〜。あーリング恋しい</t>
+          <t xml:space="preserve">連勝〜！ ノッてるね〜。この波乗りこなすぞ〜</t>
         </is>
       </c>
     </row>
     <row r="422" ht="40" customHeight="1">
       <c r="A422" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B422" t="inlineStr" s="2">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="C422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D422" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-10.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E422" t="inlineStr" s="2">
@@ -13900,14 +13900,14 @@
       </c>
       <c r="F422" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ〜、絶好調タイム終了〜。楽しかったなぁ</t>
+          <t xml:space="preserve">怪我かぁ…暇だなぁ。早く治らないかな〜</t>
         </is>
       </c>
     </row>
     <row r="423" ht="40" customHeight="1">
       <c r="A423" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B423" t="inlineStr" s="2">
@@ -13917,12 +13917,12 @@
       </c>
       <c r="C423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D423" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[2]</t>
+          <t xml:space="preserve">GL-10.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E423" t="inlineStr" s="2">
@@ -13932,14 +13932,14 @@
       </c>
       <c r="F423" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ好調もずっとは続かないよね〜。でもいい経験だった</t>
+          <t xml:space="preserve">じっとしてるの苦手なんだよね〜。あーリング恋しい</t>
         </is>
       </c>
     </row>
     <row r="424" ht="40" customHeight="1">
       <c r="A424" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B424" t="inlineStr" s="2">
@@ -13949,29 +13949,29 @@
       </c>
       <c r="C424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D424" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.easygoing[1]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F424" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、さすがに満身創痍。でもまあ、最後まで来たし、やるっきゃないでしょ</t>
+          <t xml:space="preserve">あ〜、絶好調タイム終了〜。楽しかったなぁ</t>
         </is>
       </c>
     </row>
     <row r="425" ht="40" customHeight="1">
       <c r="A425" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B425" t="inlineStr" s="2">
@@ -13981,29 +13981,29 @@
       </c>
       <c r="C425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D425" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.easygoing[2]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F425" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体ボロボロだけどさ。ここまで来て降りるとか、もったいないもんね</t>
+          <t xml:space="preserve">まぁ好調もずっとは続かないよね〜。でもいい経験だった</t>
         </is>
       </c>
     </row>
     <row r="426" ht="40" customHeight="1">
       <c r="A426" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B426" t="inlineStr" s="2">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="D426" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E426" t="inlineStr" s="2">
@@ -14028,14 +14028,14 @@
       </c>
       <c r="F426" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰かなー。まあ、来た子と真っ向勝負するっきゃないよね</t>
+          <t xml:space="preserve">いやー、さすがに満身創痍。でもまあ、最後まで来たし、やるっきゃないでしょ</t>
         </is>
       </c>
     </row>
     <row r="427" ht="40" customHeight="1">
       <c r="A427" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B427" t="inlineStr" s="2">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="D427" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E427" t="inlineStr" s="2">
@@ -14060,14 +14060,14 @@
       </c>
       <c r="F427" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よーし、あたしの番だ。止まってらんないし、いっちょやりますか</t>
+          <t xml:space="preserve">身体ボロボロだけどさ。ここまで来て降りるとか、もったいないもんね</t>
         </is>
       </c>
     </row>
     <row r="428" ht="40" customHeight="1">
       <c r="A428" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B428" t="inlineStr" s="2">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="D428" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E428" t="inlineStr" s="2">
@@ -14092,14 +14092,14 @@
       </c>
       <c r="F428" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人落としたー。…はぁ、さすがに疲れた。でもまだ立ってるよ。次、来ていいよー</t>
+          <t xml:space="preserve">相手は誰かなー。まあ、来た子と真っ向勝負するっきゃないよね</t>
         </is>
       </c>
     </row>
     <row r="429" ht="40" customHeight="1">
       <c r="A429" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B429" t="inlineStr" s="2">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="D429" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E429" t="inlineStr" s="2">
@@ -14124,14 +14124,14 @@
       </c>
       <c r="F429" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふう、一人おしまい。…でもまだ終わってないんだよね。次、早く出ておいでー</t>
+          <t xml:space="preserve">よーし、私の番だ。止まってらんないし、いっちょやりますか</t>
         </is>
       </c>
     </row>
     <row r="430" ht="40" customHeight="1">
       <c r="A430" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B430" t="inlineStr" s="2">
@@ -14141,12 +14141,12 @@
       </c>
       <c r="C430" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D430" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.easygoing[1]</t>
+          <t xml:space="preserve">survivor.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E430" t="inlineStr" s="2">
@@ -14156,14 +14156,14 @@
       </c>
       <c r="F430" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の三人だったでしょ？ 誰が欠けても、こんな景色は見られなかったよ</t>
+          <t xml:space="preserve">一人落としたー。…はぁ、さすがに疲れた。でもまだ立ってるよ。次、来ていいよー</t>
         </is>
       </c>
     </row>
     <row r="431" ht="40" customHeight="1">
       <c r="A431" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B431" t="inlineStr" s="2">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="C431" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D431" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.easygoing[2]</t>
+          <t xml:space="preserve">survivor.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E431" t="inlineStr" s="2">
@@ -14188,14 +14188,14 @@
       </c>
       <c r="F431" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝てたー！ いやー、最高の気分。今夜はお祝いだね</t>
+          <t xml:space="preserve">ふう、一人おしまい。…でもまだ終わってないんだよね。次、早く出ておいでー</t>
         </is>
       </c>
     </row>
     <row r="432" ht="40" customHeight="1">
       <c r="A432" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.easygoing[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B432" t="inlineStr" s="2">
@@ -14210,7 +14210,7 @@
       </c>
       <c r="D432" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.easygoing[3]</t>
+          <t xml:space="preserve">champion.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E432" t="inlineStr" s="2">
@@ -14220,14 +14220,14 @@
       </c>
       <c r="F432" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間がいてくれたから全然心配してなかったよ。嘘、ちょっとだけ心配だった</t>
+          <t xml:space="preserve">最高の三人だったでしょ？ 誰が欠けても、こんな景色は見られなかったよ</t>
         </is>
       </c>
     </row>
     <row r="433" ht="40" customHeight="1">
       <c r="A433" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B433" t="inlineStr" s="2">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="D433" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.easygoing[1]</t>
+          <t xml:space="preserve">champion.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E433" t="inlineStr" s="2">
@@ -14252,14 +14252,14 @@
       </c>
       <c r="F433" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPって言われても、今日は笑えないかな。次はみんなで勝ってから笑うよ</t>
+          <t xml:space="preserve">三人で勝てたー！ いやー、最高の気分。今夜はお祝いだね</t>
         </is>
       </c>
     </row>
     <row r="434" ht="40" customHeight="1">
       <c r="A434" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B434" t="inlineStr" s="2">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="D434" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.easygoing[2]</t>
+          <t xml:space="preserve">champion.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E434" t="inlineStr" s="2">
@@ -14284,14 +14284,14 @@
       </c>
       <c r="F434" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、個人賞ねぇ。まあもらっとくけど、次は三人で笑いたいな</t>
+          <t xml:space="preserve">仲間がいてくれたから全然心配してなかったよ。嘘、ちょっとだけ心配だった</t>
         </is>
       </c>
     </row>
     <row r="435" ht="40" customHeight="1">
       <c r="A435" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.easygoing[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B435" t="inlineStr" s="2">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="D435" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.easygoing[3]</t>
+          <t xml:space="preserve">defiant.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E435" t="inlineStr" s="2">
@@ -14316,14 +14316,14 @@
       </c>
       <c r="F435" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人だけ目立ってもさ、楽しくないんだよね。次はチームごと勝つよ</t>
+          <t xml:space="preserve">MVPって言われても、今日は笑えないかな。次はみんなで勝ってから笑うよ</t>
         </is>
       </c>
     </row>
     <row r="436" ht="40" customHeight="1">
       <c r="A436" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B436" t="inlineStr" s="2">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="D436" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.easygoing[1]</t>
+          <t xml:space="preserve">defiant.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E436" t="inlineStr" s="2">
@@ -14348,14 +14348,14 @@
       </c>
       <c r="F436" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人倒したら、また一人来るんだもん。途中から笑っちゃった。でも全部、楽しかったよ</t>
+          <t xml:space="preserve">いやー、個人賞ねぇ。まあもらっとくけど、次は三人で笑いたいな</t>
         </is>
       </c>
     </row>
     <row r="437" ht="40" customHeight="1">
       <c r="A437" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B437" t="inlineStr" s="2">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="D437" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.easygoing[2]</t>
+          <t xml:space="preserve">defiant.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E437" t="inlineStr" s="2">
@@ -14380,14 +14380,14 @@
       </c>
       <c r="F437" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、何人来たっけ？ 途中から数えるの諦めちゃった。あはは</t>
+          <t xml:space="preserve">一人だけ目立ってもさ、楽しくないんだよね。次はチームごと勝つよ</t>
         </is>
       </c>
     </row>
     <row r="438" ht="40" customHeight="1">
       <c r="A438" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.easygoing[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B438" t="inlineStr" s="2">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="D438" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.easygoing[3]</t>
+          <t xml:space="preserve">gauntlet.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E438" t="inlineStr" s="2">
@@ -14412,14 +14412,14 @@
       </c>
       <c r="F438" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがに足がプルプルしてる。でもまあ、全員倒したし、良しでしょ</t>
+          <t xml:space="preserve">一人倒したら、また一人来るんだもん。途中から笑っちゃった。でも全部、楽しかったよ</t>
         </is>
       </c>
     </row>
     <row r="439" ht="40" customHeight="1">
       <c r="A439" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B439" t="inlineStr" s="2">
@@ -14429,12 +14429,12 @@
       </c>
       <c r="C439" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D439" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.easygoing[1]</t>
+          <t xml:space="preserve">gauntlet.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E439" t="inlineStr" s="2">
@@ -14444,14 +14444,14 @@
       </c>
       <c r="F439" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、ほんとに勝っちゃった。最高！</t>
+          <t xml:space="preserve">いやー、何人来たっけ？ 途中から数えるの諦めちゃった。あはは</t>
         </is>
       </c>
     </row>
     <row r="440" ht="40" customHeight="1">
       <c r="A440" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B440" t="inlineStr" s="2">
@@ -14461,12 +14461,12 @@
       </c>
       <c r="C440" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D440" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.easygoing[2]</t>
+          <t xml:space="preserve">gauntlet.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E440" t="inlineStr" s="2">
@@ -14476,14 +14476,14 @@
       </c>
       <c r="F440" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっひょー！ 優勝！ 信じられない！</t>
+          <t xml:space="preserve">さすがに足がプルプルしてる。でもまあ、全員倒したし、良しでしょ</t>
         </is>
       </c>
     </row>
     <row r="441" ht="40" customHeight="1">
       <c r="A441" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B441" t="inlineStr" s="2">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="D441" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.easygoing[1]</t>
+          <t xml:space="preserve">champion.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E441" t="inlineStr" s="2">
@@ -14508,14 +14508,14 @@
       </c>
       <c r="F441" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あちゃー、負けちゃった。まあ次がんばろ</t>
+          <t xml:space="preserve">いやー、ほんとに勝っちゃった。最高！</t>
         </is>
       </c>
     </row>
     <row r="442" ht="40" customHeight="1">
       <c r="A442" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B442" t="inlineStr" s="2">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="D442" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.easygoing[2]</t>
+          <t xml:space="preserve">champion.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E442" t="inlineStr" s="2">
@@ -14540,14 +14540,14 @@
       </c>
       <c r="F442" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、しょうがないっしょ。次は勝つよ</t>
+          <t xml:space="preserve">うっひょー！ 優勝！ 信じられない！</t>
         </is>
       </c>
     </row>
     <row r="443" ht="40" customHeight="1">
       <c r="A443" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B443" t="inlineStr" s="2">
@@ -14562,7 +14562,7 @@
       </c>
       <c r="D443" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.easygoing[1]</t>
+          <t xml:space="preserve">postLose.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E443" t="inlineStr" s="2">
@@ -14572,14 +14572,14 @@
       </c>
       <c r="F443" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっし、勝った！ 次もこの調子で</t>
+          <t xml:space="preserve">あちゃー、負けちゃった。まあ次がんばろ</t>
         </is>
       </c>
     </row>
     <row r="444" ht="40" customHeight="1">
       <c r="A444" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B444" t="inlineStr" s="2">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="D444" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.easygoing[2]</t>
+          <t xml:space="preserve">postLose.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E444" t="inlineStr" s="2">
@@ -14604,14 +14604,14 @@
       </c>
       <c r="F444" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい感じいい感じ〜</t>
+          <t xml:space="preserve">ま、しょうがないっしょ。次は勝つよ</t>
         </is>
       </c>
     </row>
     <row r="445" ht="40" customHeight="1">
       <c r="A445" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B445" t="inlineStr" s="2">
@@ -14626,7 +14626,7 @@
       </c>
       <c r="D445" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.easygoing[1]</t>
+          <t xml:space="preserve">postMatchWin.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E445" t="inlineStr" s="2">
@@ -14636,14 +14636,14 @@
       </c>
       <c r="F445" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー楽しかった！ またやりたいなあ</t>
+          <t xml:space="preserve">よっし、勝った！ 次もこの調子で</t>
         </is>
       </c>
     </row>
     <row r="446" ht="40" customHeight="1">
       <c r="A446" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B446" t="inlineStr" s="2">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="D446" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.easygoing[2]</t>
+          <t xml:space="preserve">postMatchWin.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E446" t="inlineStr" s="2">
@@ -14668,14 +14668,14 @@
       </c>
       <c r="F446" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合できたし、満足満足</t>
+          <t xml:space="preserve">いい感じいい感じ〜</t>
         </is>
       </c>
     </row>
     <row r="447" ht="40" customHeight="1">
       <c r="A447" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B447" t="inlineStr" s="2">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="D447" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.easygoing[1]</t>
+          <t xml:space="preserve">postWin.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E447" t="inlineStr" s="2">
@@ -14700,14 +14700,14 @@
       </c>
       <c r="F447" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝かー。ま、ここまで来たらやるしかないっしょ</t>
+          <t xml:space="preserve">いやー楽しかった！ またやりたいなあ</t>
         </is>
       </c>
     </row>
     <row r="448" ht="40" customHeight="1">
       <c r="A448" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B448" t="inlineStr" s="2">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="D448" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.easygoing[2]</t>
+          <t xml:space="preserve">postWin.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E448" t="inlineStr" s="2">
@@ -14732,14 +14732,14 @@
       </c>
       <c r="F448" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の一戦！ 楽しむよ〜</t>
+          <t xml:space="preserve">いい試合できたし、満足満足</t>
         </is>
       </c>
     </row>
     <row r="449" ht="40" customHeight="1">
       <c r="A449" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B449" t="inlineStr" s="2">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="D449" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E449" t="inlineStr" s="2">
@@ -14764,14 +14764,14 @@
       </c>
       <c r="F449" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しんでいこう♪もちろん勝つつもりでね</t>
+          <t xml:space="preserve">決勝かー。ま、ここまで来たらやるしかないっしょ</t>
         </is>
       </c>
     </row>
     <row r="450" ht="40" customHeight="1">
       <c r="A450" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B450" t="inlineStr" s="2">
@@ -14786,7 +14786,7 @@
       </c>
       <c r="D450" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E450" t="inlineStr" s="2">
@@ -14796,14 +14796,14 @@
       </c>
       <c r="F450" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よーし、いっちょやりますか</t>
+          <t xml:space="preserve">最後の一戦！ 楽しむよ〜</t>
         </is>
       </c>
     </row>
     <row r="451" ht="40" customHeight="1">
       <c r="A451" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B451" t="inlineStr" s="2">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="D451" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E451" t="inlineStr" s="2">
@@ -14828,14 +14828,14 @@
       </c>
       <c r="F451" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、選ばれちゃった。ラッキー</t>
+          <t xml:space="preserve">楽しんでいこう♪もちろん勝つつもりでね</t>
         </is>
       </c>
     </row>
     <row r="452" ht="40" customHeight="1">
       <c r="A452" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B452" t="inlineStr" s="2">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="D452" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E452" t="inlineStr" s="2">
@@ -14860,14 +14860,14 @@
       </c>
       <c r="F452" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へー、いいじゃん。楽しそう</t>
+          <t xml:space="preserve">よーし、いっちょやりますか</t>
         </is>
       </c>
     </row>
     <row r="453" ht="40" customHeight="1">
       <c r="A453" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B453" t="inlineStr" s="2">
@@ -14877,12 +14877,12 @@
       </c>
       <c r="C453" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D453" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[1]</t>
+          <t xml:space="preserve">summon.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E453" t="inlineStr" s="2">
@@ -14892,14 +14892,14 @@
       </c>
       <c r="F453" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この大舞台、最高の気分！楽しもうぜ！</t>
+          <t xml:space="preserve">お、選ばれちゃった。ラッキー</t>
         </is>
       </c>
     </row>
     <row r="454" ht="40" customHeight="1">
       <c r="A454" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B454" t="inlineStr" s="2">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="C454" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D454" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[2]</t>
+          <t xml:space="preserve">summon.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E454" t="inlineStr" s="2">
@@ -14924,14 +14924,14 @@
       </c>
       <c r="F454" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたと戦えるの楽しみにしてた！</t>
+          <t xml:space="preserve">へー、いいじゃん。楽しそう</t>
         </is>
       </c>
     </row>
     <row r="455" ht="40" customHeight="1">
       <c r="A455" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.easygoing[3]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B455" t="inlineStr" s="2">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="D455" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[3]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E455" t="inlineStr" s="2">
@@ -14956,14 +14956,14 @@
       </c>
       <c r="F455" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すごい大舞台！これは楽しみだねっ！</t>
+          <t xml:space="preserve">この大舞台、最高の気分！ 楽しもう！</t>
         </is>
       </c>
     </row>
     <row r="456" ht="40" customHeight="1">
       <c r="A456" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B456" t="inlineStr" s="2">
@@ -14973,12 +14973,12 @@
       </c>
       <c r="C456" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D456" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[1]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E456" t="inlineStr" s="2">
@@ -14988,14 +14988,14 @@
       </c>
       <c r="F456" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっそ……マジで勝っちゃった……！ やばいやばいやばい！</t>
+          <t xml:space="preserve">あんたと戦えるの楽しみにしてた！</t>
         </is>
       </c>
     </row>
     <row r="457" ht="40" customHeight="1">
       <c r="A457" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B457" t="inlineStr" s="2">
@@ -15005,12 +15005,12 @@
       </c>
       <c r="C457" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D457" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[2]</t>
+          <t xml:space="preserve">standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E457" t="inlineStr" s="2">
@@ -15020,14 +15020,14 @@
       </c>
       <c r="F457" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、ちょっと待って……夢じゃないよね……？ 最高！</t>
+          <t xml:space="preserve">すごい大舞台！これは楽しみだねっ！</t>
         </is>
       </c>
     </row>
     <row r="458" ht="40" customHeight="1">
       <c r="A458" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.easygoing[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B458" t="inlineStr" s="2">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C458" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D458" t="inlineStr" s="12">
@@ -15052,14 +15052,14 @@
       </c>
       <c r="F458" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと遊びに来ちゃった。付き合ってよ</t>
+          <t xml:space="preserve">うっそ……マジで勝っちゃった……！ やばいやばいやばい！</t>
         </is>
       </c>
     </row>
     <row r="459" ht="40" customHeight="1">
       <c r="A459" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.easygoing[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B459" t="inlineStr" s="2">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="C459" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D459" t="inlineStr" s="12">
@@ -15084,14 +15084,14 @@
       </c>
       <c r="F459" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面白そうじゃん？ やろうよ、対抗戦</t>
+          <t xml:space="preserve">え、ちょっと待って……夢じゃないよね……？ 最高！</t>
         </is>
       </c>
     </row>
     <row r="460" ht="40" customHeight="1">
       <c r="A460" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.easygoing[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B460" t="inlineStr" s="2">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="C460" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D460" t="inlineStr" s="12">
@@ -15116,14 +15116,14 @@
       </c>
       <c r="F460" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えー、断るの？ つまんないなー</t>
+          <t xml:space="preserve">ちょっと遊びに来ちゃった。付き合ってよ</t>
         </is>
       </c>
     </row>
     <row r="461" ht="40" customHeight="1">
       <c r="A461" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.easygoing[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B461" t="inlineStr" s="2">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="C461" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D461" t="inlineStr" s="12">
@@ -15148,14 +15148,14 @@
       </c>
       <c r="F461" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあいいけどさ。気が変わったら言ってよ</t>
+          <t xml:space="preserve">面白そうじゃん？ やろうよ、対抗戦</t>
         </is>
       </c>
     </row>
     <row r="462" ht="40" customHeight="1">
       <c r="A462" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.easygoing[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B462" t="inlineStr" s="2">
@@ -15165,12 +15165,12 @@
       </c>
       <c r="C462" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D462" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.easygoing[1]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E462" t="inlineStr" s="2">
@@ -15180,14 +15180,14 @@
       </c>
       <c r="F462" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あちゃー、負けちゃったか。ま、次頑張ろ</t>
+          <t xml:space="preserve">えー、断るの？ つまんないなー</t>
         </is>
       </c>
     </row>
     <row r="463" ht="40" customHeight="1">
       <c r="A463" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.easygoing[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B463" t="inlineStr" s="2">
@@ -15197,12 +15197,12 @@
       </c>
       <c r="C463" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D463" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.easygoing[2]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E463" t="inlineStr" s="2">
@@ -15212,14 +15212,14 @@
       </c>
       <c r="F463" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドンマイドンマイ。次こそは！</t>
+          <t xml:space="preserve">まあいいけどさ。気が変わったら言ってよ</t>
         </is>
       </c>
     </row>
     <row r="464" ht="40" customHeight="1">
       <c r="A464" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B464" t="inlineStr" s="2">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="D464" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.easygoing[1]</t>
+          <t xml:space="preserve">result_lose.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E464" t="inlineStr" s="2">
@@ -15244,14 +15244,14 @@
       </c>
       <c r="F464" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったー！ 勝っちゃった！ 最高！</t>
+          <t xml:space="preserve">あちゃー、負けちゃったか。ま、次頑張ろ</t>
         </is>
       </c>
     </row>
     <row r="465" ht="40" customHeight="1">
       <c r="A465" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.easygoing[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B465" t="inlineStr" s="2">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="D465" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.easygoing[2]</t>
+          <t xml:space="preserve">result_lose.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E465" t="inlineStr" s="2">
@@ -15276,14 +15276,14 @@
       </c>
       <c r="F465" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったー！ またやろうよ</t>
+          <t xml:space="preserve">ドンマイドンマイ。次こそは！</t>
         </is>
       </c>
     </row>
     <row r="466" ht="40" customHeight="1">
       <c r="A466" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B466" t="inlineStr" s="2">
@@ -15293,12 +15293,12 @@
       </c>
       <c r="C466" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D466" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[1]</t>
+          <t xml:space="preserve">result_win.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E466" t="inlineStr" s="2">
@@ -15308,14 +15308,14 @@
       </c>
       <c r="F466" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー勝っちゃった！ うちの団体やるでしょ？</t>
+          <t xml:space="preserve">やったー！ 勝っちゃった！ 最高！</t>
         </is>
       </c>
     </row>
     <row r="467" ht="40" customHeight="1">
       <c r="A467" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B467" t="inlineStr" s="2">
@@ -15325,12 +15325,12 @@
       </c>
       <c r="C467" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D467" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[2]</t>
+          <t xml:space="preserve">result_win.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E467" t="inlineStr" s="2">
@@ -15340,14 +15340,14 @@
       </c>
       <c r="F467" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！ 対抗戦勝利！ 打ち上げ行こうよ！</t>
+          <t xml:space="preserve">楽しかったー！ またやろうよ</t>
         </is>
       </c>
     </row>
     <row r="468" ht="40" customHeight="1">
       <c r="A468" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.easygoing[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B468" t="inlineStr" s="2">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="D468" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[3]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E468" t="inlineStr" s="2">
@@ -15372,14 +15372,14 @@
       </c>
       <c r="F468" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったー！ しかも勝てたし、最高！</t>
+          <t xml:space="preserve">いやー勝っちゃった！ うちの団体やるでしょ？</t>
         </is>
       </c>
     </row>
     <row r="469" ht="40" customHeight="1">
       <c r="A469" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.easygoing[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B469" t="inlineStr" s="2">
@@ -15389,29 +15389,29 @@
       </c>
       <c r="C469" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D469" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.easygoing[1]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E469" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F469" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで掴んだ頂点だ！最高のチームだよ！</t>
+          <t xml:space="preserve">よっしゃー！ 対抗戦勝利！ 打ち上げ行こうよ！</t>
         </is>
       </c>
     </row>
     <row r="470" ht="40" customHeight="1">
       <c r="A470" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.easygoing[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B470" t="inlineStr" s="2">
@@ -15421,29 +15421,29 @@
       </c>
       <c r="C470" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D470" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.easygoing[2]</t>
+          <t xml:space="preserve">standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E470" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F470" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お金がなかった頃のことを思い出すと…よくここまで来たよね</t>
+          <t xml:space="preserve">楽しかったー！ しかも勝てたし、最高！</t>
         </is>
       </c>
     </row>
     <row r="471" ht="40" customHeight="1">
       <c r="A471" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B471" t="inlineStr" s="2">
@@ -15453,29 +15453,29 @@
       </c>
       <c r="C471" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D471" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[1]</t>
+          <t xml:space="preserve">fighter.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E471" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F471" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーも気楽だったけどねー。ここらで腰を据えるか</t>
+          <t xml:space="preserve">みんなで掴んだ頂点だ！最高のチームだよ！</t>
         </is>
       </c>
     </row>
     <row r="472" ht="40" customHeight="1">
       <c r="A472" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B472" t="inlineStr" s="2">
@@ -15485,29 +15485,29 @@
       </c>
       <c r="C472" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D472" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[2]</t>
+          <t xml:space="preserve">fighter.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E472" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F472" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声かかんなくてさー。拾ってくれて助かったよ</t>
+          <t xml:space="preserve">お金がなかった頃のことを思い出すと…よくここまで来たよね</t>
         </is>
       </c>
     </row>
     <row r="473" ht="40" customHeight="1">
       <c r="A473" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B473" t="inlineStr" s="2">
@@ -15517,7 +15517,7 @@
       </c>
       <c r="C473" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D473" t="inlineStr" s="12">
@@ -15532,44 +15532,108 @@
       </c>
       <c r="F473" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よく見つけたねー。掘り出し物だよ、あたし</t>
+          <t xml:space="preserve">フリーも気楽だったけどねー。ここらで腰を据えるか</t>
         </is>
       </c>
     </row>
     <row r="474" ht="40" customHeight="1">
       <c r="A474" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">しばらく声かかんなくてさー。呼んでくれて嬉しいよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="475" ht="40" customHeight="1">
+      <c r="A475" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よく見つけたねー。掘り出し物だよ、私</t>
+        </is>
+      </c>
+    </row>
+    <row r="476" ht="40" customHeight="1">
+      <c r="A476" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.standard.easygoing[2]</t>
         </is>
       </c>
-      <c r="B474" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr" s="2">
+      <c r="B476" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr" s="12">
+      <c r="D476" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
-      <c r="E474" t="inlineStr" s="2">
+      <c r="E476" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F474" t="inlineStr" s="3">
+      <c r="F476" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ちょうど暴れる場所探してたんだ。よろしくね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H474"/>
+  <autoFilter ref="A1:H476"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×お気楽.xlsx
@@ -372,7 +372,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H476"/>
+  <dimension ref="A1:H478"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -13491,7 +13491,7 @@
     <row r="410" ht="40" customHeight="1">
       <c r="A410" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="D410" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E410" t="inlineStr" s="2">
@@ -13516,14 +13516,14 @@
       </c>
       <c r="F410" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習たのし〜。いい汗かいてるわ</t>
+          <t xml:space="preserve">うーん…なんか気になっちゃうなあ、あの子のこと</t>
         </is>
       </c>
     </row>
     <row r="411" ht="40" customHeight="1">
       <c r="A411" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="D411" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.easygoing[2]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E411" t="inlineStr" s="2">
@@ -13548,14 +13548,14 @@
       </c>
       <c r="F411" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よーし、今日もがんばるぞ〜っと</t>
+          <t xml:space="preserve">あいつのこと考えると力入っちゃうわ。まあいっか</t>
         </is>
       </c>
     </row>
     <row r="412" ht="40" customHeight="1">
       <c r="A412" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="D412" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-02.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E412" t="inlineStr" s="2">
@@ -13580,14 +13580,14 @@
       </c>
       <c r="F412" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ〜？ なんかちょっと居心地悪くなった？</t>
+          <t xml:space="preserve">練習たのし〜。いい汗かいてるわ</t>
         </is>
       </c>
     </row>
     <row r="413" ht="40" customHeight="1">
       <c r="A413" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="D413" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-02.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E413" t="inlineStr" s="2">
@@ -13612,14 +13612,14 @@
       </c>
       <c r="F413" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近めっちゃ楽しい〜。ここ大好き！</t>
+          <t xml:space="preserve">よーし、今日もがんばるぞ〜っと</t>
         </is>
       </c>
     </row>
     <row r="414" ht="40" customHeight="1">
       <c r="A414" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="D414" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-03.down.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E414" t="inlineStr" s="2">
@@ -13644,14 +13644,14 @@
       </c>
       <c r="F414" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒だとテンション上がるわ〜</t>
+          <t xml:space="preserve">あれ〜？ なんかちょっと居心地悪くなった？</t>
         </is>
       </c>
     </row>
     <row r="415" ht="40" customHeight="1">
       <c r="A415" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="D415" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-03.up.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E415" t="inlineStr" s="2">
@@ -13676,14 +13676,14 @@
       </c>
       <c r="F415" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気になって仕方ないんだよね〜</t>
+          <t xml:space="preserve">最近めっちゃ楽しい〜。ここ大好き！</t>
         </is>
       </c>
     </row>
     <row r="416" ht="40" customHeight="1">
       <c r="A416" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="D416" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-04.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E416" t="inlineStr" s="2">
@@ -13708,14 +13708,14 @@
       </c>
       <c r="F416" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ今週は仕方ないか〜。でもちょっと寂しいな</t>
+          <t xml:space="preserve">一緒だとテンション上がるわ〜</t>
         </is>
       </c>
     </row>
     <row r="417" ht="40" customHeight="1">
       <c r="A417" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B417" t="inlineStr" s="2">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="D417" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.easygoing[2]</t>
+          <t xml:space="preserve">GL-05.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E417" t="inlineStr" s="2">
@@ -13740,14 +13740,14 @@
       </c>
       <c r="F417" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お休みかぁ。まぁたまにはね。…うん、寂しいけど</t>
+          <t xml:space="preserve">気になって仕方ないんだよね〜</t>
         </is>
       </c>
     </row>
     <row r="418" ht="40" customHeight="1">
       <c r="A418" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B418" t="inlineStr" s="2">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="D418" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-06.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E418" t="inlineStr" s="2">
@@ -13772,14 +13772,14 @@
       </c>
       <c r="F418" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、体がだるいなぁ。ちょっと休もっかな</t>
+          <t xml:space="preserve">まあ今週は仕方ないか〜。でもちょっと寂しいな</t>
         </is>
       </c>
     </row>
     <row r="419" ht="40" customHeight="1">
       <c r="A419" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B419" t="inlineStr" s="2">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="D419" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-06.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E419" t="inlineStr" s="2">
@@ -13804,14 +13804,14 @@
       </c>
       <c r="F419" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは…笑えない状況だね…さすがに凹むわ</t>
+          <t xml:space="preserve">お休みかぁ。まぁたまにはね。…うん、寂しいけど</t>
         </is>
       </c>
     </row>
     <row r="420" ht="40" customHeight="1">
       <c r="A420" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B420" t="inlineStr" s="2">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="D420" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.easygoing[2]</t>
+          <t xml:space="preserve">GL-07.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E420" t="inlineStr" s="2">
@@ -13836,14 +13836,14 @@
       </c>
       <c r="F420" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、負けが込んでるなぁ…どうしたもんか</t>
+          <t xml:space="preserve">う〜ん、体がだるいなぁ。ちょっと休もっかな</t>
         </is>
       </c>
     </row>
     <row r="421" ht="40" customHeight="1">
       <c r="A421" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B421" t="inlineStr" s="2">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="D421" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-08.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E421" t="inlineStr" s="2">
@@ -13868,14 +13868,14 @@
       </c>
       <c r="F421" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝〜！ ノッてるね〜。この波乗りこなすぞ〜</t>
+          <t xml:space="preserve">あはは…笑えない状況だね…さすがに凹むわ</t>
         </is>
       </c>
     </row>
     <row r="422" ht="40" customHeight="1">
       <c r="A422" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B422" t="inlineStr" s="2">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="D422" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-08.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E422" t="inlineStr" s="2">
@@ -13900,14 +13900,14 @@
       </c>
       <c r="F422" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我かぁ…暇だなぁ。早く治らないかな〜</t>
+          <t xml:space="preserve">う〜ん、負けが込んでるなぁ…どうしたもんか</t>
         </is>
       </c>
     </row>
     <row r="423" ht="40" customHeight="1">
       <c r="A423" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B423" t="inlineStr" s="2">
@@ -13922,7 +13922,7 @@
       </c>
       <c r="D423" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.easygoing[2]</t>
+          <t xml:space="preserve">GL-09.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E423" t="inlineStr" s="2">
@@ -13932,14 +13932,14 @@
       </c>
       <c r="F423" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">じっとしてるの苦手なんだよね〜。あーリング恋しい</t>
+          <t xml:space="preserve">連勝〜！ ノッてるね〜。この波乗りこなすぞ〜</t>
         </is>
       </c>
     </row>
     <row r="424" ht="40" customHeight="1">
       <c r="A424" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B424" t="inlineStr" s="2">
@@ -13949,12 +13949,12 @@
       </c>
       <c r="C424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D424" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[1]</t>
+          <t xml:space="preserve">GL-10.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E424" t="inlineStr" s="2">
@@ -13964,14 +13964,14 @@
       </c>
       <c r="F424" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ〜、絶好調タイム終了〜。楽しかったなぁ</t>
+          <t xml:space="preserve">怪我かぁ…暇だなぁ。早く治らないかな〜</t>
         </is>
       </c>
     </row>
     <row r="425" ht="40" customHeight="1">
       <c r="A425" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B425" t="inlineStr" s="2">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="C425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D425" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[2]</t>
+          <t xml:space="preserve">GL-10.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E425" t="inlineStr" s="2">
@@ -13996,14 +13996,14 @@
       </c>
       <c r="F425" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ好調もずっとは続かないよね〜。でもいい経験だった</t>
+          <t xml:space="preserve">じっとしてるの苦手なんだよね〜。あーリング恋しい</t>
         </is>
       </c>
     </row>
     <row r="426" ht="40" customHeight="1">
       <c r="A426" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B426" t="inlineStr" s="2">
@@ -14013,29 +14013,29 @@
       </c>
       <c r="C426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D426" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.easygoing[1]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F426" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、さすがに満身創痍。でもまあ、最後まで来たし、やるっきゃないでしょ</t>
+          <t xml:space="preserve">あ〜、絶好調タイム終了〜。楽しかったなぁ</t>
         </is>
       </c>
     </row>
     <row r="427" ht="40" customHeight="1">
       <c r="A427" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B427" t="inlineStr" s="2">
@@ -14045,29 +14045,29 @@
       </c>
       <c r="C427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D427" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.easygoing[2]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F427" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体ボロボロだけどさ。ここまで来て降りるとか、もったいないもんね</t>
+          <t xml:space="preserve">まぁ好調もずっとは続かないよね〜。でもいい経験だった</t>
         </is>
       </c>
     </row>
     <row r="428" ht="40" customHeight="1">
       <c r="A428" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B428" t="inlineStr" s="2">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="D428" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E428" t="inlineStr" s="2">
@@ -14092,14 +14092,14 @@
       </c>
       <c r="F428" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手は誰かなー。まあ、来た子と真っ向勝負するっきゃないよね</t>
+          <t xml:space="preserve">いやー、さすがに満身創痍。でもまあ、最後まで来たし、やるっきゃないでしょ</t>
         </is>
       </c>
     </row>
     <row r="429" ht="40" customHeight="1">
       <c r="A429" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B429" t="inlineStr" s="2">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="D429" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E429" t="inlineStr" s="2">
@@ -14124,14 +14124,14 @@
       </c>
       <c r="F429" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よーし、私の番だ。止まってらんないし、いっちょやりますか</t>
+          <t xml:space="preserve">身体ボロボロだけどさ。ここまで来て降りるとか、もったいないもんね</t>
         </is>
       </c>
     </row>
     <row r="430" ht="40" customHeight="1">
       <c r="A430" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B430" t="inlineStr" s="2">
@@ -14146,7 +14146,7 @@
       </c>
       <c r="D430" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E430" t="inlineStr" s="2">
@@ -14156,14 +14156,14 @@
       </c>
       <c r="F430" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人落としたー。…はぁ、さすがに疲れた。でもまだ立ってるよ。次、来ていいよー</t>
+          <t xml:space="preserve">相手は誰かなー。まあ、来た子と真っ向勝負するっきゃないよね</t>
         </is>
       </c>
     </row>
     <row r="431" ht="40" customHeight="1">
       <c r="A431" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B431" t="inlineStr" s="2">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="D431" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E431" t="inlineStr" s="2">
@@ -14188,14 +14188,14 @@
       </c>
       <c r="F431" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふう、一人おしまい。…でもまだ終わってないんだよね。次、早く出ておいでー</t>
+          <t xml:space="preserve">よーし、私の番だ。止まってらんないし、いっちょやりますか</t>
         </is>
       </c>
     </row>
     <row r="432" ht="40" customHeight="1">
       <c r="A432" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B432" t="inlineStr" s="2">
@@ -14205,12 +14205,12 @@
       </c>
       <c r="C432" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D432" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.easygoing[1]</t>
+          <t xml:space="preserve">survivor.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E432" t="inlineStr" s="2">
@@ -14220,14 +14220,14 @@
       </c>
       <c r="F432" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の三人だったでしょ？ 誰が欠けても、こんな景色は見られなかったよ</t>
+          <t xml:space="preserve">一人落としたー。…はぁ、さすがに疲れた。でもまだ立ってるよ。次、来ていいよー</t>
         </is>
       </c>
     </row>
     <row r="433" ht="40" customHeight="1">
       <c r="A433" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B433" t="inlineStr" s="2">
@@ -14237,12 +14237,12 @@
       </c>
       <c r="C433" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D433" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.easygoing[2]</t>
+          <t xml:space="preserve">survivor.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E433" t="inlineStr" s="2">
@@ -14252,14 +14252,14 @@
       </c>
       <c r="F433" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で勝てたー！ いやー、最高の気分。今夜はお祝いだね</t>
+          <t xml:space="preserve">ふう、一人おしまい。…でもまだ終わってないんだよね。次、早く出ておいでー</t>
         </is>
       </c>
     </row>
     <row r="434" ht="40" customHeight="1">
       <c r="A434" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.easygoing[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B434" t="inlineStr" s="2">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="D434" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.easygoing[3]</t>
+          <t xml:space="preserve">champion.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E434" t="inlineStr" s="2">
@@ -14284,14 +14284,14 @@
       </c>
       <c r="F434" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間がいてくれたから全然心配してなかったよ。嘘、ちょっとだけ心配だった</t>
+          <t xml:space="preserve">最高の三人だったでしょ？ 誰が欠けても、こんな景色は見られなかったよ</t>
         </is>
       </c>
     </row>
     <row r="435" ht="40" customHeight="1">
       <c r="A435" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B435" t="inlineStr" s="2">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="D435" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.easygoing[1]</t>
+          <t xml:space="preserve">champion.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E435" t="inlineStr" s="2">
@@ -14316,14 +14316,14 @@
       </c>
       <c r="F435" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPって言われても、今日は笑えないかな。次はみんなで勝ってから笑うよ</t>
+          <t xml:space="preserve">三人で勝てたー！ いやー、最高の気分。今夜はお祝いだね</t>
         </is>
       </c>
     </row>
     <row r="436" ht="40" customHeight="1">
       <c r="A436" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B436" t="inlineStr" s="2">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="D436" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.easygoing[2]</t>
+          <t xml:space="preserve">champion.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E436" t="inlineStr" s="2">
@@ -14348,14 +14348,14 @@
       </c>
       <c r="F436" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、個人賞ねぇ。まあもらっとくけど、次は三人で笑いたいな</t>
+          <t xml:space="preserve">仲間がいてくれたから全然心配してなかったよ。嘘、ちょっとだけ心配だった</t>
         </is>
       </c>
     </row>
     <row r="437" ht="40" customHeight="1">
       <c r="A437" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.easygoing[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B437" t="inlineStr" s="2">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="D437" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.easygoing[3]</t>
+          <t xml:space="preserve">defiant.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E437" t="inlineStr" s="2">
@@ -14380,14 +14380,14 @@
       </c>
       <c r="F437" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人だけ目立ってもさ、楽しくないんだよね。次はチームごと勝つよ</t>
+          <t xml:space="preserve">MVPって言われても、今日は笑えないかな。次はみんなで勝ってから笑うよ</t>
         </is>
       </c>
     </row>
     <row r="438" ht="40" customHeight="1">
       <c r="A438" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B438" t="inlineStr" s="2">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="D438" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.easygoing[1]</t>
+          <t xml:space="preserve">defiant.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E438" t="inlineStr" s="2">
@@ -14412,14 +14412,14 @@
       </c>
       <c r="F438" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人倒したら、また一人来るんだもん。途中から笑っちゃった。でも全部、楽しかったよ</t>
+          <t xml:space="preserve">いやー、個人賞ねぇ。まあもらっとくけど、次は三人で笑いたいな</t>
         </is>
       </c>
     </row>
     <row r="439" ht="40" customHeight="1">
       <c r="A439" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B439" t="inlineStr" s="2">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="D439" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.easygoing[2]</t>
+          <t xml:space="preserve">defiant.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E439" t="inlineStr" s="2">
@@ -14444,14 +14444,14 @@
       </c>
       <c r="F439" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、何人来たっけ？ 途中から数えるの諦めちゃった。あはは</t>
+          <t xml:space="preserve">一人だけ目立ってもさ、楽しくないんだよね。次はチームごと勝つよ</t>
         </is>
       </c>
     </row>
     <row r="440" ht="40" customHeight="1">
       <c r="A440" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.easygoing[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B440" t="inlineStr" s="2">
@@ -14466,7 +14466,7 @@
       </c>
       <c r="D440" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.easygoing[3]</t>
+          <t xml:space="preserve">gauntlet.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E440" t="inlineStr" s="2">
@@ -14476,14 +14476,14 @@
       </c>
       <c r="F440" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがに足がプルプルしてる。でもまあ、全員倒したし、良しでしょ</t>
+          <t xml:space="preserve">一人倒したら、また一人来るんだもん。途中から笑っちゃった。でも全部、楽しかったよ</t>
         </is>
       </c>
     </row>
     <row r="441" ht="40" customHeight="1">
       <c r="A441" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B441" t="inlineStr" s="2">
@@ -14493,12 +14493,12 @@
       </c>
       <c r="C441" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D441" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.easygoing[1]</t>
+          <t xml:space="preserve">gauntlet.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E441" t="inlineStr" s="2">
@@ -14508,14 +14508,14 @@
       </c>
       <c r="F441" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、ほんとに勝っちゃった。最高！</t>
+          <t xml:space="preserve">いやー、何人来たっけ？ 途中から数えるの諦めちゃった。あはは</t>
         </is>
       </c>
     </row>
     <row r="442" ht="40" customHeight="1">
       <c r="A442" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B442" t="inlineStr" s="2">
@@ -14525,12 +14525,12 @@
       </c>
       <c r="C442" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D442" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.easygoing[2]</t>
+          <t xml:space="preserve">gauntlet.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E442" t="inlineStr" s="2">
@@ -14540,14 +14540,14 @@
       </c>
       <c r="F442" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっひょー！ 優勝！ 信じられない！</t>
+          <t xml:space="preserve">さすがに足がプルプルしてる。でもまあ、全員倒したし、良しでしょ</t>
         </is>
       </c>
     </row>
     <row r="443" ht="40" customHeight="1">
       <c r="A443" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B443" t="inlineStr" s="2">
@@ -14562,7 +14562,7 @@
       </c>
       <c r="D443" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.easygoing[1]</t>
+          <t xml:space="preserve">champion.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E443" t="inlineStr" s="2">
@@ -14572,14 +14572,14 @@
       </c>
       <c r="F443" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あちゃー、負けちゃった。まあ次がんばろ</t>
+          <t xml:space="preserve">いやー、ほんとに勝っちゃった。最高！</t>
         </is>
       </c>
     </row>
     <row r="444" ht="40" customHeight="1">
       <c r="A444" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B444" t="inlineStr" s="2">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="D444" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.easygoing[2]</t>
+          <t xml:space="preserve">champion.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E444" t="inlineStr" s="2">
@@ -14604,14 +14604,14 @@
       </c>
       <c r="F444" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、しょうがないっしょ。次は勝つよ</t>
+          <t xml:space="preserve">うっひょー！ 優勝！ 信じられない！</t>
         </is>
       </c>
     </row>
     <row r="445" ht="40" customHeight="1">
       <c r="A445" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B445" t="inlineStr" s="2">
@@ -14626,7 +14626,7 @@
       </c>
       <c r="D445" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.easygoing[1]</t>
+          <t xml:space="preserve">postLose.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E445" t="inlineStr" s="2">
@@ -14636,14 +14636,14 @@
       </c>
       <c r="F445" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっし、勝った！ 次もこの調子で</t>
+          <t xml:space="preserve">あちゃー、負けちゃった。まあ次がんばろ</t>
         </is>
       </c>
     </row>
     <row r="446" ht="40" customHeight="1">
       <c r="A446" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B446" t="inlineStr" s="2">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="D446" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.easygoing[2]</t>
+          <t xml:space="preserve">postLose.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E446" t="inlineStr" s="2">
@@ -14668,14 +14668,14 @@
       </c>
       <c r="F446" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい感じいい感じ〜</t>
+          <t xml:space="preserve">ま、しょうがないっしょ。次は勝つよ</t>
         </is>
       </c>
     </row>
     <row r="447" ht="40" customHeight="1">
       <c r="A447" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B447" t="inlineStr" s="2">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="D447" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.easygoing[1]</t>
+          <t xml:space="preserve">postMatchWin.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E447" t="inlineStr" s="2">
@@ -14700,14 +14700,14 @@
       </c>
       <c r="F447" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー楽しかった！ またやりたいなあ</t>
+          <t xml:space="preserve">よっし、勝った！ 次もこの調子で</t>
         </is>
       </c>
     </row>
     <row r="448" ht="40" customHeight="1">
       <c r="A448" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B448" t="inlineStr" s="2">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="D448" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.easygoing[2]</t>
+          <t xml:space="preserve">postMatchWin.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E448" t="inlineStr" s="2">
@@ -14732,14 +14732,14 @@
       </c>
       <c r="F448" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合できたし、満足満足</t>
+          <t xml:space="preserve">いい感じいい感じ〜</t>
         </is>
       </c>
     </row>
     <row r="449" ht="40" customHeight="1">
       <c r="A449" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B449" t="inlineStr" s="2">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="D449" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.easygoing[1]</t>
+          <t xml:space="preserve">postWin.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E449" t="inlineStr" s="2">
@@ -14764,14 +14764,14 @@
       </c>
       <c r="F449" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝かー。ま、ここまで来たらやるしかないっしょ</t>
+          <t xml:space="preserve">いやー楽しかった！ またやりたいなあ</t>
         </is>
       </c>
     </row>
     <row r="450" ht="40" customHeight="1">
       <c r="A450" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B450" t="inlineStr" s="2">
@@ -14786,7 +14786,7 @@
       </c>
       <c r="D450" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.easygoing[2]</t>
+          <t xml:space="preserve">postWin.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E450" t="inlineStr" s="2">
@@ -14796,14 +14796,14 @@
       </c>
       <c r="F450" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の一戦！ 楽しむよ〜</t>
+          <t xml:space="preserve">いい試合できたし、満足満足</t>
         </is>
       </c>
     </row>
     <row r="451" ht="40" customHeight="1">
       <c r="A451" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B451" t="inlineStr" s="2">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="D451" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E451" t="inlineStr" s="2">
@@ -14828,14 +14828,14 @@
       </c>
       <c r="F451" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しんでいこう♪もちろん勝つつもりでね</t>
+          <t xml:space="preserve">決勝かー。ま、ここまで来たらやるしかないっしょ</t>
         </is>
       </c>
     </row>
     <row r="452" ht="40" customHeight="1">
       <c r="A452" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B452" t="inlineStr" s="2">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="D452" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E452" t="inlineStr" s="2">
@@ -14860,14 +14860,14 @@
       </c>
       <c r="F452" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よーし、いっちょやりますか</t>
+          <t xml:space="preserve">最後の一戦！ 楽しむよ〜</t>
         </is>
       </c>
     </row>
     <row r="453" ht="40" customHeight="1">
       <c r="A453" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B453" t="inlineStr" s="2">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="D453" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E453" t="inlineStr" s="2">
@@ -14892,14 +14892,14 @@
       </c>
       <c r="F453" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、選ばれちゃった。ラッキー</t>
+          <t xml:space="preserve">楽しんでいこう♪もちろん勝つつもりでね</t>
         </is>
       </c>
     </row>
     <row r="454" ht="40" customHeight="1">
       <c r="A454" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B454" t="inlineStr" s="2">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="D454" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E454" t="inlineStr" s="2">
@@ -14924,14 +14924,14 @@
       </c>
       <c r="F454" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へー、いいじゃん。楽しそう</t>
+          <t xml:space="preserve">よーし、いっちょやりますか</t>
         </is>
       </c>
     </row>
     <row r="455" ht="40" customHeight="1">
       <c r="A455" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B455" t="inlineStr" s="2">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="C455" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D455" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[1]</t>
+          <t xml:space="preserve">summon.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E455" t="inlineStr" s="2">
@@ -14956,14 +14956,14 @@
       </c>
       <c r="F455" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この大舞台、最高の気分！ 楽しもう！</t>
+          <t xml:space="preserve">お、選ばれちゃった。ラッキー</t>
         </is>
       </c>
     </row>
     <row r="456" ht="40" customHeight="1">
       <c r="A456" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B456" t="inlineStr" s="2">
@@ -14973,12 +14973,12 @@
       </c>
       <c r="C456" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D456" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[2]</t>
+          <t xml:space="preserve">summon.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E456" t="inlineStr" s="2">
@@ -14988,14 +14988,14 @@
       </c>
       <c r="F456" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたと戦えるの楽しみにしてた！</t>
+          <t xml:space="preserve">へー、いいじゃん。楽しそう</t>
         </is>
       </c>
     </row>
     <row r="457" ht="40" customHeight="1">
       <c r="A457" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.easygoing[3]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B457" t="inlineStr" s="2">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="D457" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[3]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E457" t="inlineStr" s="2">
@@ -15020,14 +15020,14 @@
       </c>
       <c r="F457" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すごい大舞台！これは楽しみだねっ！</t>
+          <t xml:space="preserve">この大舞台、最高の気分！ 楽しもう！</t>
         </is>
       </c>
     </row>
     <row r="458" ht="40" customHeight="1">
       <c r="A458" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B458" t="inlineStr" s="2">
@@ -15037,12 +15037,12 @@
       </c>
       <c r="C458" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D458" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[1]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E458" t="inlineStr" s="2">
@@ -15052,14 +15052,14 @@
       </c>
       <c r="F458" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うっそ……マジで勝っちゃった……！ やばいやばいやばい！</t>
+          <t xml:space="preserve">あんたと戦えるの楽しみにしてた！</t>
         </is>
       </c>
     </row>
     <row r="459" ht="40" customHeight="1">
       <c r="A459" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B459" t="inlineStr" s="2">
@@ -15069,12 +15069,12 @@
       </c>
       <c r="C459" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D459" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[2]</t>
+          <t xml:space="preserve">standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E459" t="inlineStr" s="2">
@@ -15084,14 +15084,14 @@
       </c>
       <c r="F459" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、ちょっと待って……夢じゃないよね……？ 最高！</t>
+          <t xml:space="preserve">すごい大舞台！これは楽しみだねっ！</t>
         </is>
       </c>
     </row>
     <row r="460" ht="40" customHeight="1">
       <c r="A460" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.easygoing[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B460" t="inlineStr" s="2">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="C460" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D460" t="inlineStr" s="12">
@@ -15116,14 +15116,14 @@
       </c>
       <c r="F460" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと遊びに来ちゃった。付き合ってよ</t>
+          <t xml:space="preserve">うっそ……マジで勝っちゃった……！ やばいやばいやばい！</t>
         </is>
       </c>
     </row>
     <row r="461" ht="40" customHeight="1">
       <c r="A461" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.easygoing[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B461" t="inlineStr" s="2">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="C461" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D461" t="inlineStr" s="12">
@@ -15148,14 +15148,14 @@
       </c>
       <c r="F461" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面白そうじゃん？ やろうよ、対抗戦</t>
+          <t xml:space="preserve">え、ちょっと待って……夢じゃないよね……？ 最高！</t>
         </is>
       </c>
     </row>
     <row r="462" ht="40" customHeight="1">
       <c r="A462" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.easygoing[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B462" t="inlineStr" s="2">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="C462" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D462" t="inlineStr" s="12">
@@ -15180,14 +15180,14 @@
       </c>
       <c r="F462" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えー、断るの？ つまんないなー</t>
+          <t xml:space="preserve">ちょっと遊びに来ちゃった。付き合ってよ</t>
         </is>
       </c>
     </row>
     <row r="463" ht="40" customHeight="1">
       <c r="A463" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.easygoing[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B463" t="inlineStr" s="2">
@@ -15197,7 +15197,7 @@
       </c>
       <c r="C463" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D463" t="inlineStr" s="12">
@@ -15212,14 +15212,14 @@
       </c>
       <c r="F463" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあいいけどさ。気が変わったら言ってよ</t>
+          <t xml:space="preserve">面白そうじゃん？ やろうよ、対抗戦</t>
         </is>
       </c>
     </row>
     <row r="464" ht="40" customHeight="1">
       <c r="A464" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.easygoing[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B464" t="inlineStr" s="2">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="C464" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D464" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.easygoing[1]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E464" t="inlineStr" s="2">
@@ -15244,14 +15244,14 @@
       </c>
       <c r="F464" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あちゃー、負けちゃったか。ま、次頑張ろ</t>
+          <t xml:space="preserve">えー、断るの？ つまんないなー</t>
         </is>
       </c>
     </row>
     <row r="465" ht="40" customHeight="1">
       <c r="A465" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.easygoing[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B465" t="inlineStr" s="2">
@@ -15261,12 +15261,12 @@
       </c>
       <c r="C465" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D465" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.easygoing[2]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E465" t="inlineStr" s="2">
@@ -15276,14 +15276,14 @@
       </c>
       <c r="F465" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドンマイドンマイ。次こそは！</t>
+          <t xml:space="preserve">まあいいけどさ。気が変わったら言ってよ</t>
         </is>
       </c>
     </row>
     <row r="466" ht="40" customHeight="1">
       <c r="A466" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B466" t="inlineStr" s="2">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="D466" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.easygoing[1]</t>
+          <t xml:space="preserve">result_lose.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E466" t="inlineStr" s="2">
@@ -15308,14 +15308,14 @@
       </c>
       <c r="F466" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったー！ 勝っちゃった！ 最高！</t>
+          <t xml:space="preserve">あちゃー、負けちゃったか。ま、次頑張ろ</t>
         </is>
       </c>
     </row>
     <row r="467" ht="40" customHeight="1">
       <c r="A467" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.easygoing[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B467" t="inlineStr" s="2">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="D467" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.easygoing[2]</t>
+          <t xml:space="preserve">result_lose.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E467" t="inlineStr" s="2">
@@ -15340,14 +15340,14 @@
       </c>
       <c r="F467" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったー！ またやろうよ</t>
+          <t xml:space="preserve">ドンマイドンマイ。次こそは！</t>
         </is>
       </c>
     </row>
     <row r="468" ht="40" customHeight="1">
       <c r="A468" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B468" t="inlineStr" s="2">
@@ -15357,12 +15357,12 @@
       </c>
       <c r="C468" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D468" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[1]</t>
+          <t xml:space="preserve">result_win.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E468" t="inlineStr" s="2">
@@ -15372,14 +15372,14 @@
       </c>
       <c r="F468" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー勝っちゃった！ うちの団体やるでしょ？</t>
+          <t xml:space="preserve">やったー！ 勝っちゃった！ 最高！</t>
         </is>
       </c>
     </row>
     <row r="469" ht="40" customHeight="1">
       <c r="A469" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B469" t="inlineStr" s="2">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="C469" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D469" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[2]</t>
+          <t xml:space="preserve">result_win.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E469" t="inlineStr" s="2">
@@ -15404,14 +15404,14 @@
       </c>
       <c r="F469" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よっしゃー！ 対抗戦勝利！ 打ち上げ行こうよ！</t>
+          <t xml:space="preserve">楽しかったー！ またやろうよ</t>
         </is>
       </c>
     </row>
     <row r="470" ht="40" customHeight="1">
       <c r="A470" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.easygoing[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B470" t="inlineStr" s="2">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="D470" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[3]</t>
+          <t xml:space="preserve">standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E470" t="inlineStr" s="2">
@@ -15436,14 +15436,14 @@
       </c>
       <c r="F470" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったー！ しかも勝てたし、最高！</t>
+          <t xml:space="preserve">いやー勝っちゃった！ うちの団体やるでしょ？</t>
         </is>
       </c>
     </row>
     <row r="471" ht="40" customHeight="1">
       <c r="A471" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.easygoing[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B471" t="inlineStr" s="2">
@@ -15453,29 +15453,29 @@
       </c>
       <c r="C471" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D471" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.easygoing[1]</t>
+          <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E471" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F471" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで掴んだ頂点だ！最高のチームだよ！</t>
+          <t xml:space="preserve">よっしゃー！ 対抗戦勝利！ 打ち上げ行こうよ！</t>
         </is>
       </c>
     </row>
     <row r="472" ht="40" customHeight="1">
       <c r="A472" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.easygoing[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.easygoing[3]</t>
         </is>
       </c>
       <c r="B472" t="inlineStr" s="2">
@@ -15485,29 +15485,29 @@
       </c>
       <c r="C472" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D472" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.easygoing[2]</t>
+          <t xml:space="preserve">standard.easygoing[3]</t>
         </is>
       </c>
       <c r="E472" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F472" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お金がなかった頃のことを思い出すと…よくここまで来たよね</t>
+          <t xml:space="preserve">楽しかったー！ しかも勝てたし、最高！</t>
         </is>
       </c>
     </row>
     <row r="473" ht="40" customHeight="1">
       <c r="A473" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B473" t="inlineStr" s="2">
@@ -15517,29 +15517,29 @@
       </c>
       <c r="C473" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D473" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[1]</t>
+          <t xml:space="preserve">fighter.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="E473" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F473" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーも気楽だったけどねー。ここらで腰を据えるか</t>
+          <t xml:space="preserve">みんなで掴んだ頂点だ！最高のチームだよ！</t>
         </is>
       </c>
     </row>
     <row r="474" ht="40" customHeight="1">
       <c r="A474" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.easygoing[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="B474" t="inlineStr" s="2">
@@ -15549,29 +15549,29 @@
       </c>
       <c r="C474" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D474" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.easygoing[2]</t>
+          <t xml:space="preserve">fighter.standard.easygoing[2]</t>
         </is>
       </c>
       <c r="E474" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F474" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しばらく声かかんなくてさー。呼んでくれて嬉しいよ</t>
+          <t xml:space="preserve">お金がなかった頃のことを思い出すと…よくここまで来たよね</t>
         </is>
       </c>
     </row>
     <row r="475" ht="40" customHeight="1">
       <c r="A475" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.easygoing[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.easygoing[1]</t>
         </is>
       </c>
       <c r="B475" t="inlineStr" s="2">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="C475" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D475" t="inlineStr" s="12">
@@ -15596,44 +15596,108 @@
       </c>
       <c r="F475" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よく見つけたねー。掘り出し物だよ、私</t>
+          <t xml:space="preserve">フリーも気楽だったけどねー。ここらで腰を据えるか</t>
         </is>
       </c>
     </row>
     <row r="476" ht="40" customHeight="1">
       <c r="A476" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">しばらく声かかんなくてさー。呼んでくれて嬉しいよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="477" ht="40" customHeight="1">
+      <c r="A477" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よく見つけたねー。掘り出し物だよ、私</t>
+        </is>
+      </c>
+    </row>
+    <row r="478" ht="40" customHeight="1">
+      <c r="A478" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.standard.easygoing[2]</t>
         </is>
       </c>
-      <c r="B476" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr" s="2">
+      <c r="B478" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr" s="12">
+      <c r="D478" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard.easygoing[2]</t>
         </is>
       </c>
-      <c r="E476" t="inlineStr" s="2">
+      <c r="E478" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F476" t="inlineStr" s="3">
+      <c r="F478" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ちょうど暴れる場所探してたんだ。よろしくね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H476"/>
+  <autoFilter ref="A1:H478"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×お気楽.xlsx
@@ -2983,7 +2983,7 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あの人とやってみたいんですけど、どうですか。</t>
+          <t xml:space="preserve">社長、三人であちらへ行ってみたいんですけど、どうですか。</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">だめならいいんです。でも、あの人とやりたくて。</t>
+          <t xml:space="preserve">だめならいいんです。でも、三人で挑んでみたくて。</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんとなく、あの人とやりたくなっちゃって。</t>
+          <t xml:space="preserve">なんとなく、三人で乗り込みたくなっちゃって。</t>
         </is>
       </c>
     </row>
